--- a/spiderOkx/欧易数据.xlsx
+++ b/spiderOkx/欧易数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7575"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="718">
   <si>
     <t>发布时间</t>
   </si>
@@ -36,6 +36,15 @@
   </si>
   <si>
     <t>帖子内容</t>
+  </si>
+  <si>
+    <t>涉及币种</t>
+  </si>
+  <si>
+    <t>开仓点位</t>
+  </si>
+  <si>
+    <t>帖子观点</t>
   </si>
   <si>
     <t>2026-07-23 18:27:28</t>
@@ -46,6 +55,12 @@
   <si>
     <t>熊市结束了，这次熊市结束是Bitmex交易所倒闭收尾，不过很体面不是跑路。4年前（2022）熊市结束是FTX交易所跑路收尾。
 狗庄给你们6万U整数第三次抄底比特币的概率下降为50%。#BTC #BitMEX</t>
+  </si>
+  <si>
+    <t>['BTC']</t>
+  </si>
+  <si>
+    <t>看多</t>
   </si>
   <si>
     <t>2026-07-23 14:17:46</t>
@@ -57,6 +72,9 @@
     <t>当你挑战做一件难的事
 如同往天平抬起的一边加水
 一滴一滴没有任何变化，但是当你一直坚持，加到最后那一滴，你会发现量变会瞬间引发质变</t>
+  </si>
+  <si>
+    <t>中性</t>
   </si>
   <si>
     <t>2026-07-23 17:22:21</t>
@@ -77,6 +95,9 @@
 如果你想改善你的入场点，保存这篇帖子。</t>
   </si>
   <si>
+    <t>['PLTR', 'AMD', 'AVGO', 'ORCL', 'MU', 'TSM', 'MRVL', 'NVDA', 'CL']</t>
+  </si>
+  <si>
     <t>2026-07-23 21:12:06</t>
   </si>
   <si>
@@ -93,6 +114,9 @@
 #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
   </si>
   <si>
+    <t>['NVDA', 'GOOGL', 'TSLA']</t>
+  </si>
+  <si>
     <t>2026-07-23 18:01:00</t>
   </si>
   <si>
@@ -100,6 +124,12 @@
   </si>
   <si>
     <t>特斯拉交付量超预期，财报却没接住！ 2Q26 火线速读： 汽车利润承压，储能毛利腰斩，Robotaxi 和 Optimus 仍然停留在“讲未来”。 交付量大超预期之后，市场把对这次财报的期待拉得很高。 但结果是：营收基本符合预期，利润却明显不及预期。 营收还行，但毛利率崩了 特斯拉二季度营收 282 亿美元，同比增长 25.5%，基本符合市场预期的 281 亿美元。 但整体毛利率只有 16.8%，环比下降 4.3 个百分点，也低于预期的 19.5%。 营收增长主要靠卖得更多，利润却没有同步跟上。 #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？  卖车收入增长，但单车越来越不赚钱 二季度汽车收入约 200 亿美元，同比增长 27%，主要由销量同比增长 25%带动。 问题是，单车售价仍在下降。 本季度平均售价约 4.2 万美元，环比下降 1,300 美元。 原因包括： 产品组合向低价车型倾斜，Model S/X 停产； 促销优惠抵消了车型提价； 美国市场占比下降，欧洲及其他地区占比提升，区域结构也带来负面影响。 剔除碳积分和租赁收入后，特斯拉真实汽车毛利率只有 16.3%。 即使销量大</t>
+  </si>
+  <si>
+    <t>['TSLA', 'GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'TSLA', '点位': 1300.0}]</t>
   </si>
   <si>
     <t>2026-07-23 14:04:47</t>
@@ -133,6 +163,9 @@
 目前预计 2026 年的资本支出（Capex）为 1950 亿至 2050 亿美元。此外，Gemini 目前的月活跃用户数已达 9.5 亿，略低于 ChatGPT。</t>
   </si>
   <si>
+    <t>['SPCX', 'NVDA', 'GOOGL', 'AMD']</t>
+  </si>
+  <si>
     <t>2026-07-23 13:51:37</t>
   </si>
   <si>
@@ -159,6 +192,9 @@
 7 月 23 日，ARK Invest 旗下基金合计买入 12.14 万股 SpaceX 股票，价值约 1499.6 万美元；同时卖出 9.73 万股 Robinhood 股票，价值约 1035.1 万美元，延续近期减持趋势。ARK 当日还买入约 496.5 万美元的电动飞行器公司 Archer Aviation 股票。  $SPCX</t>
   </si>
   <si>
+    <t>['SPCX']</t>
+  </si>
+  <si>
     <t>2026-07-22 11:47:05</t>
   </si>
   <si>
@@ -179,6 +215,12 @@
 随着做空者平仓，价格迅速反弹，重新回到了0.060美元左右的支撑位。</t>
   </si>
   <si>
+    <t>['WLFI']</t>
+  </si>
+  <si>
+    <t>看空</t>
+  </si>
+  <si>
     <t>2026-07-23 18:13:30</t>
   </si>
   <si>
@@ -199,10 +241,16 @@
     <t>Kimi K3 发布的这一周，美国科技圈都在集体惋惜，杨植麟这样一个优秀的年轻人，为什么当年没有留在美国。 Kimi K3 在前端能力上超越所有模型 这个话题在 X 上拿到了五百多万次浏览。特朗普之前的白宫 AI 领头人 David Sacks，即特朗普的直属亲信，都说自己已经从 Claude 切到了 Kimi 处理大量工作，「它就是好玩得多，因为它直接干活而不是对你说教」。而硅谷老牌风投 Vinod Khosla 把账算到移民政策头上，说美国正在亲手把杰出人才吓跑。 猜测越滚越大，杨植麟的博士生导师 Salakhutdinov 一边在社交媒体上公开「秀」爱徒，一边为杨植麟澄清没有留在美国的原因：「如果连尝试创业的勇气都没有，杨植麟说他会后悔一辈子。」 在大洋这一边，还有另一个广东人的名字，也为中国 AI 圈广为人知，梁文锋。 梁文锋比杨植麟大七岁，生在湛江吴川，一个做了十五年量化交易的程序员，几乎没接受过采访，没有社交账号，同事对他唯一的人格概括是「除了编程没有什么其他爱好」。2025 年 1 月他的 DeepSeek R1 发布后，英伟达一天蒸发近 6000 亿美元市值，硅谷管那叫</t>
   </si>
   <si>
+    <t>['NVDA']</t>
+  </si>
+  <si>
     <t>2026-07-23 14:57:11</t>
   </si>
   <si>
     <t>Long 生态币股概念 Meme 逆势拉升，AI 市值达到 1500 万美元，SPACEHOOD 市值突破 100 万美元。 #交易之声：你的经验值得被听到  撰文：KarenZ，Foresight News 如果一枚 Meme 用英伟达股票代币定价，会发生什么？ 过去，链上新币通常与链上原生代币（如 ETH、SOL 等）、稳定币或发射台平台币（如 Virtuals）组成交易池。现在，Robinhood Chain 上出现了一类新的交易对：社区币的一侧仍是 Meme 或项目代币，另一侧则换成英伟达、苹果、特斯拉、SpaceX 等股票代币。 于是，一枚代币不再只显示「值多少美元」，还可以显示「相比英伟达表现如何」。 这项涉及看似只是换了一个交易对，实际却把股票代币从一种供人持有和交易的资产，变成了链上市场的计价单位、流动性资产和费用资产。 Long 先把股票代币带进了 Launchpad Long 于 2025 年 5 月份在 Base 上首次推出，由创始人 Nate（@Natan_benish）推动，早期重点是动态拍卖和公平发行。 一年后的 2026 年 5 月 28 日，Long 宣</t>
+  </si>
+  <si>
+    <t>['SPCX', 'ETH', 'SOL', 'TSLA', 'NVDA']</t>
   </si>
   <si>
     <t>2026-07-23 17:19:12</t>
@@ -219,6 +267,9 @@
 总结一句话就是这出戏远没到高潮。油价多头逻辑铁硬！只要特朗普还没喊“不打了”，就继续逢低吸纳，拿住核心筹码，别被日内洗盘震出去。
 加密玩家还是老实点儿，降杠杆、控仓位，盯紧白宫和德黑兰的下一步动作。局势不缓和，降息预期别想快速升温，大饼想持续反弹？门儿都没有。
 局势不彻底明朗前，拿住筹码等风来才是最稳妥的！</t>
+  </si>
+  <si>
+    <t>['BZ', 'BTC', 'CL']</t>
   </si>
   <si>
     <t>2026-07-23 15:01:36</t>
@@ -272,6 +323,12 @@
 $BTC #ETH #BTC #Crypto</t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'SNDK', 'MU', 'TSLA', 'INTC', 'HYPE', 'SKHY', 'GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 16.86}]</t>
+  </si>
+  <si>
     <t>2026-07-20 18:37:15</t>
   </si>
   <si>
@@ -279,6 +336,9 @@
   </si>
   <si>
     <t>WhiteLine Daily 是吴说区块链推出的新栏目，聚焦 AI 时代的全球市场与科技产业，关注这些变化如何影响加密市场和资产定价，并用更容易理解的方式提炼每天最值得关注的市场线索。 01｜市场焦点｜长鑫存储 5792 亿估值，市场到底在买哪一年利润 长鑫科技发行价为 8.66 元，对应上市估值约 5792 亿元，基础募资约 579 亿元。网上申购倍数达到 243.93 倍，最终中签率为 0.4714%，预计 7 月 27 日正式上市。 表面看，这是市场对稀缺国产 DRAM 资产的一次集中认购；真正的矛盾在于，应该用哪一年的利润给长鑫估值。 按 2025 年利润计算，长鑫的发行市盈率超过 300 倍，市净率约为 5 倍。但公司 2026 年一季度净利润已经达到 330 亿元，预计上半年净利润为 660 亿—750 亿元。 按历史利润看很贵，按当前周期的利润看又显得便宜。这意味着市场正在判断：2026 年的高利润会成为新的盈利平台，还是只属于这一轮存储周期的顶部。 长鑫 2025 年的全球 DRAM 市场份额约为 7.7%，已经成为三星电子、SK 海力士和美光之外的第四家规模化厂商。</t>
+  </si>
+  <si>
+    <t>['MU', 'SKHY']</t>
   </si>
   <si>
     <t>2026-07-23 15:12:04</t>
@@ -393,10 +453,19 @@
 AI 的故事还在继续，但从现在开始，资本会越来越认真地看 ROI。</t>
   </si>
   <si>
+    <t>['GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'GOOGL', '点位': 9.11}, {'币种': 'GOOGL', '点位': 1950.0}, {'币种': 'GOOGL', '点位': 2050.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 15:06:21</t>
   </si>
   <si>
     <t>据 Onchain Lens 监测，疑似属于 Multicoin Capital 的地址过去两日累计转移约 49 万枚 HYPE，价值约 2948 万美元。其中，39.75 万枚 HYPE 经多个地址转移后最终存入 Coinbase；最新又有 9.3 万枚 HYPE 转入两个新地址。</t>
+  </si>
+  <si>
+    <t>['COIN', 'HYPE']</t>
   </si>
   <si>
     <t>2026-07-23 21:51:26</t>
@@ -410,6 +479,9 @@
 $KAITO最近一个月连续上涨，涨幅超过100%了。
 这种情况猜测是OKX的玩家，借币砸盘，等跌下来再买回来还上。(OKX用户还是会玩啊)
 但是Kaito与X和解了，新的内容即将推出，应该是一波利好。</t>
+  </si>
+  <si>
+    <t>['KAITO']</t>
   </si>
   <si>
     <t>2026-07-23 22:11:33</t>
@@ -430,10 +502,19 @@
 #KOSPI破7000，韩国加密交易量降89% </t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'SOL', 'SKHY']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'ETH', '点位': 7000.0}, {'币种': 'BTC', '点位': 64943.6}]</t>
+  </si>
+  <si>
     <t>2026-07-23 11:09:24</t>
   </si>
   <si>
     <t>"拿着不动就行"，这句话简单，但现货市场里，真正靠"不动"跑赢时间的人并不多。问题不在"要不要拿住"，而在更前面。选的币、拿的方式、用的策略、看周期的角度，任何一步走偏，"拿着不动"就无从谈起。 选币：这笔钱适不适合长期拿着 "拿着不动跑赢时间"，对一类资产成立：本身有长期价值支撑的资产。比特币、以太坊拿几年不动，靠的是市场地位支撑；一个短时热点炒起来的新币、没什么实际用途的山寨币，拿着换来的不是增值，是慢慢归零。追热点时想的是"先上车再说"，上车之后却用主流币那套"越跌越是机会"的心态去套。两种逻辑不一样，套用错了，自然跑不赢时间。 还有容易被忽略的维度。一是流动性：盘子小、深度差的币，即便你真心想长期拿着，一旦急需资金，也未必能顺利卖出，变成"被迫拿着"而不是"主动拿着"，这跟"甘愿长期持有"是两回事。二是叙事集中度：只押注单一热点赛道的一个币，一旦这个叙事退潮，长期持有就失去了支撑。真正适合长期拿着的，往往是不依赖某个短期叙事、本身站得住的资产。 持仓心态：仓位大小和资金性质，决定能不能拿住 同样是浮亏，仓位轻的人能扛，仓位重的人整晚睡不着。心态好不好，很大程度不是性格问题，是仓</t>
+  </si>
+  <si>
+    <t>['BTC', 'ETH']</t>
   </si>
   <si>
     <t>2026-07-23 16:30:40</t>
@@ -462,6 +543,9 @@
 他说哪怕你还没赚到钱，只要脑子里想的是“我要垄断、我要暴利”，你就已经输了。OpenAI今天的困境就源于此，当初想独占AI，所以一定会被无数人围攻。反过来，DeepSeek主动放弃暴利、最强模型开源、不抢用户、不搞垄断，反而赢面最大。这套逻辑把整个商业世界的常识都翻过来了</t>
   </si>
   <si>
+    <t>[{'币种': 'NVDA', '点位': 15.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 11:20:12</t>
   </si>
   <si>
@@ -472,6 +556,12 @@
 今天以太坊又回到1920附近，短线重点关注 1950-1960 压力区，以及 1880-1900 支撑区。
 如果冲击 1950-1960 后无法有效突破，可以考虑轻仓尝试空单，目标看 1920 → 1900，跌破 1900再看 1870附近。
 如果放量突破 1960 并站稳，空头思路失效，不过日内先不考虑破2000的可能！</t>
+  </si>
+  <si>
+    <t>['ETH']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'ETH', '点位': 1870.0}, {'币种': 'ETH', '点位': 1880.0}, {'币种': 'ETH', '点位': 1900.0}, {'币种': 'ETH', '点位': 1920.0}, {'币种': 'ETH', '点位': 1950.0}]</t>
   </si>
   <si>
     <t>2026-07-23 17:55:28</t>
@@ -531,6 +621,9 @@
 $BTC $UNI #板块轮动 #资金流向 #KOSPI</t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'UNI', 'HYPE']</t>
+  </si>
+  <si>
     <t>2026-07-21 17:56:46</t>
   </si>
   <si>
@@ -539,6 +632,12 @@
   <si>
     <t>7月21日，美股收盘后，此前被Kimi K3搅得人心惶惶的芯片板块，终于缓过了一口气。 市场一度担心的"DeepSeek 2.0时刻"并没有进一步发酵。SK海力士虽然仍收跌1.86%，但闪迪、美光等此前的明星标的已经转头向上，出现了企稳反弹的迹象。整个半导体板块在经历了一周多的猛烈抛售之后，似乎找到了一个暂时的平衡点。 为什么这一次，Kimi K3没有复制DeepSeek 1.0时的恐慌剧本？
  一、K3的叙事变了：不是"算力够用"，而是"算力紧缺" DeepSeek 1.0之所以能在去年三四月份掀起轩然大波，核心叙事是"低成本、高效率、算力不紧缺"——它用极少的GPU资源训练出了接近顶级水平的模型，直接冲击了"AI性能必须靠疯狂堆芯片"的投资逻辑。 但Kimi K3的故事完全不同。 K3虽然以2.8万亿参数和极低的单次推理成本震惊业界，但它发布后的另一个副作用同样引人注目：算力紧缺。K3的火爆程度超出了预期，导致月之暗面的推理基础设施迅速承压，算力扩容成为当务之急。 这意味着什么？意味着K3不是在证明"不需要那么多芯片"，而是在证明"即便模型效率再高，需求增长的速度永远会跑在供给前面</t>
+  </si>
+  <si>
+    <t>['MU', 'SKHY', 'SNDK']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'MU', '点位': 3.0}]</t>
   </si>
   <si>
     <t>2026-07-20 18:35:12</t>
@@ -577,6 +676,9 @@
 如果資料來源之間互相矛盾，我會先標記衝突，等原始公告或下一個時間點確認，不用社交媒體的情緒替代證據。這也意味著有些時候最好的操作是空倉等待，因為沒有交易本身也是對不確定性的管理。</t>
   </si>
   <si>
+    <t>[{'币种': 'BTC', '点位': 6.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 10:56:46</t>
   </si>
   <si>
@@ -584,6 +686,9 @@
 问题来了：这规矩要是早两年立，某位懂王家的 meme 币，还能顺顺当当收割那一整波吗？
 如果通过，那已经发行的 $WLFI$TRUMP 之类的又怎么算？
 懂王：堂下何人状告本官？😝</t>
+  </si>
+  <si>
+    <t>['TRUMP', 'WLFI']</t>
   </si>
   <si>
     <t>2026-07-23 13:49:59</t>
@@ -602,6 +707,9 @@
 $SNDK </t>
   </si>
   <si>
+    <t>['SNDK']</t>
+  </si>
+  <si>
     <t>2026-07-21 12:33:39</t>
   </si>
   <si>
@@ -617,6 +725,9 @@
     <t>🥲近期链上多注意安全！Verus 以太坊跨链桥遭受攻击，损失约 754 万美元资金
 据 @blockaid_  监测，其已检测到 @VerusCoin  以太坊跨链桥遭受攻击，损失约 754 万美元资金，
 涉及资产包括 $ETH、tBTC、 $USDC 、 $USDT 、EURC、 $MKR 和 scrvUSD 。</t>
+  </si>
+  <si>
+    <t>['COIN', 'BTC', 'ETH']</t>
   </si>
   <si>
     <t>2026-07-23 13:11:06</t>
@@ -656,6 +767,9 @@
 市场随后可能会震荡，然后渐渐启动。</t>
   </si>
   <si>
+    <t>[{'币种': 'BTC', '点位': 55.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 20:08:49</t>
   </si>
   <si>
@@ -675,6 +789,12 @@
 盘后财报出来的瞬间，XGOOGL和XTSLA直接开动。谷歌盘后跌超4%，代币化美股7乘24小时全天候交易，不需要等第二天开盘，基于最新收盘价加市场预估就能直接交易。如果你在等传统美股开盘再反应，黄花菜都凉了。代币化美股的精髓就是交易时间的自由，财报、地缘、政策，任何非交易时段的消息都能即时反应，不拖、不等、不浪费情绪。
 对BTC的影响有两层。短期看，谷歌盘后跌超4%会压制科技股情绪，BTC作为高贝塔资产可能被拖累，66000附近震荡加剧。中期看，AI资本开支持续扩张，债务和开支都在膨胀，烧的是法币信用，强化的是BTC的非主权资产叙事。特斯拉持有BTC不变，不买不卖，长期配置逻辑没变。
 刺哥说完了。财报验证了AI需求，也验证了烧钱速度，市场需要时间消化。拿住仓位，别被财报波动晃下车。你细品。#财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ $BTC $ETH $SOL </t>
+  </si>
+  <si>
+    <t>['BTC', 'ETH', 'SOL', 'TSLA', 'GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 66000.0}]</t>
   </si>
   <si>
     <t>2026-07-23 16:34:22</t>
@@ -735,10 +855,16 @@
 #代币化股票月转账量一年增170倍 </t>
   </si>
   <si>
+    <t>['MU', 'NVDA', 'SKHY', 'TSLA']</t>
+  </si>
+  <si>
     <t>2026-07-21 17:57:56</t>
   </si>
   <si>
     <t>作者：Zhou，ChainCatcher   最近，BIP-110 把比特币社区重新拉回一场熟悉又陌生的争论。 熟悉的是，争议仍围绕链上任意数据、铭文、Runes、OP_RETURN 和节点本身展开。陌生的是，这次下场的人不再只有开发者和节点运营者。 Strategy 创始人 Michael Saylor、Blockstream 联合创始人 Adam Back、矿池 Foundry 与 Ocean、Bitcoin Knots 节点阵营，以及 Ordinals 生态参与者，都从不同方向介入了这场争论。 7 月 18 日，Michael Saylor 在长文《110 Reasons BIP-110 Is a Bad Idea》中列出 110 条理由反对 BIP-110。他认为，这一提案会把垃圾数据之争升级为共识规则变更，并让部分当前有效、且愿意支付手续费的交易失效。 这让 BIP-110 不再只是一个技术提案。它开始逼问比特币社区一个更底层的问题，谁有权决定 Bitcoin 应该是什么。   BIP-110 是什么：把反垃圾从转发策略推到共识层 BIP-110 全称为 Reduced Da</t>
+  </si>
+  <si>
+    <t>['COIN', 'BTC']</t>
   </si>
   <si>
     <t>2026-07-23 20:22:58</t>
@@ -758,6 +884,9 @@
 $BZ $CL </t>
   </si>
   <si>
+    <t>['BZ', 'CL']</t>
+  </si>
+  <si>
     <t>2026-07-23 18:12:36</t>
   </si>
   <si>
@@ -767,6 +896,12 @@
 BTC上涨压力66000（昨天测试5次都站稳）、只有企稳66000一晚上才会继续上涨冲击67788，一定要敢在夏季结束前抄底，不然贝莱德后面筹码吸够了你们都会踏空。#BTC
 ETH空了3次虽然吃肉但是没有大跌，一旦跌破1900会直接干到1888、1818.不过中线目标2100还是有盼头的。
 闪迪SNDK涨的很猛，如果能盘整重新测试1418的缺口上涨更好（听过有1500地板空的还没解套），1888是最大的压力缺口套牢盘这里非常多。#SNDK</t>
+  </si>
+  <si>
+    <t>['BTC', 'SNDK']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 8.0}, {'币种': 'BTC', '点位': 10.0}, {'币种': 'BTC', '点位': 200.0}, {'币种': 'BTC', '点位': 64588.0}, {'币种': 'BTC', '点位': 66666.0}]</t>
   </si>
   <si>
     <t>2026-07-21 15:18:59</t>
@@ -791,6 +926,12 @@
 反正我看这事儿，表面是"资金搬家"，里子是"投机情绪的迁移"。韩国散户没变，还是那批敢赌的人，只是换了个赌场。但赌场换了，赌性没换。哪天AI芯片的故事炒不动了，这批钱又会跑回币圈，或者跑去下一个能讲故事的地方。
 7000点的KOSPI，3亿美元的加密日交易量，这两个数字放在一起，不是在说"股市赢了、币圈输了"，而是在说——韩国的热钱，永远在找下一个能让自己翻倍的地方。
 纯属个人瞎琢磨，不构成任何投资建议，两边都有风险，自己掂量。</t>
+  </si>
+  <si>
+    <t>['BTC', 'GOOGL', 'SKHY']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'GOOGL', '点位': 7000.0}]</t>
   </si>
   <si>
     <t>2026-07-22 17:34:27</t>
@@ -835,10 +976,16 @@
 7 月 23 日，Multicoin Capital 管理合伙人 Tushar Jain 表示：解除质押大量 $HYPE 并非为了出售，链上隐私对机构至关重要</t>
   </si>
   <si>
+    <t>[{'币种': 'COIN', '点位': 7.0}, {'币种': 'COIN', '点位': 10.0}]</t>
+  </si>
+  <si>
     <t>2026-07-21 16:15:41</t>
   </si>
   <si>
     <t>编者按：英文区拥有 50 万粉丝的博主“Doctor Profit”，曾精准预测 2025 年 BTC 顶部（12.6 万美元），大举做空 100 多个山寨币并持续做空获利，甚至预测 BTC 将跌到 3 至 4 万美元。 然而，上周六，“Doctor Profit”发布最新推文称，近期已平仓所有空单，并重新买入比特币现货，计划在 5.4 万至 6.4 万美元区间定投。他给出原因：一是市场情绪极度悲观，散户一致等待 4 万至 5 万美元的“四年周期底部”，而自己选择抢跑，认为底部会提前到来；二是比特币正面临结构性巨变——代币化试点（贝莱德、高盛等参与）、CLARITY 法案推进、机构资本加速入场，这些因素正瓦解更深崩盘的条件；三是加密熊市已持续九个月，而股市刚见顶，崩盘资金可能流向低估的加密市场。 该博文已在 X 平台获得 230 万阅读量，以下是原文内容，由 Odaily星球日报 编译，Enjoy～ —————————— 今天，我将发布自 2025 年 9 月逃顶以来最重大的操作之一——我已平仓所有加密货币空头头寸。 在 11.5 万美元至 12.5 万美元之间建立的比特币空头头寸现已</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 230.0}]</t>
   </si>
   <si>
     <t>2026-07-23 21:58:00</t>
@@ -863,6 +1010,9 @@
 因为华尔街那帮人不傻。他们看得懂——一旦CLARITY法案通过，美国本土的加密创新将大规模回流。 过去几年多少开发者去了新加坡、迪拜？就因为他们不敢在美国写代码。
 现在好了，安全港一落地，开发者不用跑了。
 隐私协议、去中心化钱包、DeFi协议——这些赛道的项目估值，可能面临全面重估。$BTC #参议院发布CLARITY新文本，最快下周表决 </t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 1.14}]</t>
   </si>
   <si>
     <t>2026-07-23 09:22:36</t>
@@ -895,6 +1045,9 @@
 若支撑失守，修复行情阶段性承压。走势密切跟随纳指与全球存储板块联动表现，不宜高位追涨。#美股全线走高，加密股领涨 #KOSPI大涨5.85%，芯片逼空反弹 #伦理条款获特朗普认可，分歧仍存 </t>
   </si>
   <si>
+    <t>[{'币种': 'MU', '点位': 915.0}, {'币种': 'MU', '点位': 935.0}, {'币种': 'MU', '点位': 936.0}, {'币种': 'MU', '点位': 980.0}, {'币种': 'MU', '点位': 982.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 12:26:53</t>
   </si>
   <si>
@@ -935,6 +1088,12 @@
 【风险提示：仅个人交易记录分享，不构成任何投资建议】</t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'CL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'CL', '点位': 640.0}, {'币种': 'CL', '点位': 645.0}, {'币种': 'CL', '点位': 653.0}, {'币种': 'CL', '点位': 655.0}, {'币种': 'CL', '点位': 656.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 19:04:51</t>
   </si>
   <si>
@@ -944,6 +1103,9 @@
     <t xml:space="preserve">财报是市场最直接的晴雨表，谷歌和特斯拉数据落地后股价双双下挫，说明现在的市场已经不满足于营收增长，开始追问AI投入什么时候才能变成利润和现金流。
 接下来几场更关键，7月30日Meta、微软、高通集中交卷，分别检验AI应用、云算力和端侧AI；7月31日轮到苹果、亚马逊和Coinbase，对应消费电子、云计算和加密市场；8月4日至5日的Palantir和AMD，则要回答AI软件订单能不能追上估值，以及英伟达之外的AI芯片需求到底有多强。
 最后是8月27日凌晨的英伟达，基本算是本轮AI财报季的总决赛。接下来一个月，市场交易的不会只是业绩超不超预期，而是哪条AI路线已经开始赚钱，哪家公司还在靠资本开支撑估值，会很精彩。$GOOGL  $TSLA </t>
+  </si>
+  <si>
+    <t>['NVDA', 'GOOGL', 'TSLA', 'AMD']</t>
   </si>
   <si>
     <t>2026-07-23 15:01:07</t>
@@ -978,6 +1140,12 @@
     <t>无限子弹？七月以来累计建仓超 1.09 亿美元 $ETH 和 $WBTC 的巨鲸再囤 1775 万美元资产😵
 过去 4 小时从交易所提出 75 WBTC 和 4998 ETH，截至目前已累计建仓 56400 枚 ETH 和 700 枚 WBTC，总价值 1.48 亿美元，平均成本约为 $1742 和 $64205，浮盈 1142 万美元
 钱包地址 0x268448f31594F4636D03cBB4E813b94801E47643</t>
+  </si>
+  <si>
+    <t>['BTC', 'ETH', 'WBTC']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'ETH', '点位': 1742.0}]</t>
   </si>
   <si>
     <t>2026-07-23 22:13:02</t>
@@ -994,6 +1162,12 @@
 第三，华尔街巨头全下场了。DTCC在Canton网络完成代币化国债和股票测试交易，计划10月全面推出，目标是接入DTC托管的114万亿美元资产。纽交所母公司跟OKX成立合资公司，Coinbase和币安也上线了代币化美股产品。
 盘面现在65000附近晃，这事儿短期对大饼价格影响有限，但长期是趋势信号。传统金融正在把资产往链上搬，加密生态的底层价值在变厚。所以中长期角度来看，这样对比特币算基本面的利好！
 关注法老，财富不迷路！$BTC $LAB $SOL #代币化股票月转账量一年增170倍 </t>
+  </si>
+  <si>
+    <t>['LAB', 'BTC', 'SOL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 65000.0}]</t>
   </si>
   <si>
     <t>2026-07-23 15:16:26</t>
@@ -1051,6 +1225,12 @@
 这里有一点要强调，双币赢不是理财产品，不要被超高收益的行权价蛊惑，高收益意味着高风险。这是一场人性的博弈，行权的位置一定是你能坦然接受的位置，不要既想要高收益又不想承担风险最后怪产品。</t>
   </si>
   <si>
+    <t>['MU', 'TSLA']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'MU', '点位': 47.0}, {'币种': 'MU', '点位': 820.0}, {'币种': 'MU', '点位': 959.0}, {'币种': 'MU', '点位': 10000.0}, {'币种': 'MU', '点位': 10047.0}]</t>
+  </si>
+  <si>
     <t>2026-07-22 17:19:32</t>
   </si>
   <si>
@@ -1066,6 +1246,9 @@
     <t>特斯拉财报没啥好看的，如果作为一个纯车企来看早就贵到离谱了，尤其是SpaceX上市之后高科技旗舰的风头也被抢走了，毕竟在地球上开车的故事没有登陆火星性感。
 电话会上富国银行分析师Langan直接提问了合并，马斯克的回答是：“合并这种事不能在财报电话会上谈——必须走适当的流程”），同时强调两家公司的重叠"越来越多"。但是要注意的是“can't talk about it here”不意味着“no”，适当的流程（appropriate process）是并购的术语级用词，这已经不是暗示而是明示了。
 同时马斯克表示未来Starlink将装进所有特斯拉车型（不只Cybertruck）、Terafab“将是一个巨型项目”、车载Grok由SpaceXAI提供、Cybercab依赖Starlink联网、SpaceXAI在开发Optimus的管理者AI模型。这些明面上的合作甚至可以说是两家公司合并前的有意磨合。$TSLA  $SPCX  #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？  #</t>
+  </si>
+  <si>
+    <t>['SPCX', 'TSLA', 'GOOGL']</t>
   </si>
   <si>
     <t>2026-07-23 20:33:58</t>
@@ -1098,6 +1281,9 @@
  #美股全线走高，加密股领涨 </t>
   </si>
   <si>
+    <t>[{'币种': 'SPCX', '点位': 115.26}, {'币种': 'SPCX', '点位': 135.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 20:50:12</t>
   </si>
   <si>
@@ -1124,6 +1310,9 @@
 此前市场普遍认为开启转化后有25%的额度，这条新闻直接让全市场的认知多了一个小数点——预期额度直接缩水了10倍。这导致了ADR的稀缺性提高，溢价自然也再次提高。
 但实际上这条信息4天前的7.19-20号就已经在韩国社区流传了，但彼时股价仍在下跌，剧烈的去杠杆痛苦下没人在意这条新闻。同时下跌行情中这种逆势消息也自然会被过滤掉。今天谷歌的资本开支托住硬件厂商的股价之后市场自然会去寻找原因，这条本来不被重视，但是该知道的人早就知道的信息被再次注意后快速破圈变成所有人都知道所有人知道的信息从而进一步发酵最终导致盘前逼空。
 但关键仍然是今晚美股开盘后能否站稳并且明天韩股开盘后能否继续延续这条利好所带来的上涨。如果涨了，说明市场仍有多余买盘，跌了，那这条消息就是高点开空的窗口。消息与行情的双涡轮驱动模型里，最关键的永远是燃料够不够而不是打不打火。$SKHY  #KOSPI破7000，韩国加密交易量降89% </t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 7.19}, {'币种': 'BTC', '点位': 20.0}]</t>
   </si>
   <si>
     <t>2026-07-23 22:03:07</t>
@@ -1150,6 +1339,12 @@
 0x8ab1：7 月 20 日开立，以 10 倍逐仓持有 19,225 份，价值约 199.54 万美元，均价 100.2 美元，浮盈约 6.8 万美元，回报率约 35.7%；
  0x32d7：以 5 倍逐仓持有 11,604.1 份，价值约 120.4 万美元，均价 100.2 美元，浮盈约 4.1 万美元，回报率约 17.9%。
 其中 0x8ab1 与 0x32d7 账户均仅持有 INTC，未配置其他标的；三名多头目前均无 INTC 公开挂单，财报前仓位暂时落定。 #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
+  </si>
+  <si>
+    <t>['INTC', 'TSLA', 'GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'INTC', '点位': 94.5}, {'币种': 'INTC', '点位': 97.7}, {'币种': 'INTC', '点位': 100.2}, {'币种': 'INTC', '点位': 103.79}]</t>
   </si>
   <si>
     <t>2026-07-23 14:48:05</t>
@@ -1215,6 +1410,9 @@
 #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
   </si>
   <si>
+    <t>[{'币种': 'SPCX', '点位': 2.85}, {'币种': 'SPCX', '点位': 2.89}, {'币种': 'SPCX', '点位': 1800.0}, {'币种': 'SPCX', '点位': 1900.0}, {'币种': 'SPCX', '点位': 1950.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 19:22:01</t>
   </si>
   <si>
@@ -1234,6 +1432,9 @@
 要知道ADR 比韩国本土股一度溢价 51%、现在还持续在 30+%。
 这与芯片代工巨头台积电(TSM.N)如出一辙，套利者要小心了！
 继续永远缺存储！🫡</t>
+  </si>
+  <si>
+    <t>['SKHY', 'TSM']</t>
   </si>
   <si>
     <t>2026-07-23 14:46:52</t>
@@ -1281,6 +1482,9 @@
 #KOSPI破7000，韩国加密交易量降89% </t>
   </si>
   <si>
+    <t>['SKHY']</t>
+  </si>
+  <si>
     <t>2026-07-23 18:29:42</t>
   </si>
   <si>
@@ -1303,6 +1507,9 @@
     <t>杨植麟说，如果他不至少尝试一次自己创业，他会后悔一辈子。#Kimi K3 #AI 摘要：2026年7月16日，月之暗面正式推出Kimi K3。Kimi K3在能力上已接近美国前沿人工智能实验室Anthropic所开发的模型。这一进展表明，中美两国在最先进人工智能领域的差距正不断缩小。 一、Kimi K3概览 据《Kimi K3：智能的新前沿》介绍，Kimi K3 是一个 2.8 万亿参数模型，基于 KDA 混合线性注意力机制（Kimi Delta Attention）和注意力残差（Attention Residuals）技术构建，原生支持视觉理解，并拥有 100 万 token 上下文窗口。它是全球首个开源的 3 万亿级别模型，面向长程编程、知识工作和推理等前沿智能场景而设计。 虽然 Kimi K3 的整体表现仍落后于最强的闭源模型 Claude Fable 5 和 GPT-5.6 Sol，但它在整套评测中展现出前沿水平的能力，并稳定超过了其他所有模型。 Kimi K3 基于 Kimi Delta Attention（KDA）和 Attention Residuals（AttnRes）</t>
   </si>
   <si>
+    <t>['SOL']</t>
+  </si>
+  <si>
     <t>2026-07-22 15:26:43</t>
   </si>
   <si>
@@ -1317,10 +1524,16 @@
 $BTC #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
   </si>
   <si>
+    <t>['BTC', 'GOOGL', 'TSLA']</t>
+  </si>
+  <si>
     <t>2026-07-23 17:38:58</t>
   </si>
   <si>
     <t>北京时间 7 月 22 日晨，谷歌母公司 Alphabet 于美股盘后公布了 2026 年第二季度财报。 如果单纯从业绩数字来看，这是一份近乎完美的成绩单。Q2，Alphabet 实现营收 1198 亿美元，同比增长 24%，营业利润达 408 亿美元，同比增长 30% —— 公司已连续第 12 个季度保持双位数营收增长，核心业务依旧展现出极强的增长韧性。 Odaily 注：如上表所示，很多投资者都看到了谷歌本季度 9.11 美元的炸裂 EPS（每股净收入），强调该数据远高于去年同期的 2.31 美元，但这主要是因为计入了 14% Anthropic 股权的估值增长，若剔除相关收益后 EPS 仅为 2.85 美元，低于市场预期的 2.95 美元。 其中，最受市场关注的 Google Cloud 更是交出了一份远超预期的答卷。上季度，谷歌云业务收入达到 247.7 亿美元，同比增长 82%，成为 Alphabet 增长最快的业务板块。 与此同时，谷歌传统基本盘依旧稳固，Google Services 收入 945.4 亿美元，同比增长 15%，其中搜索及其他业务收入 632.7 亿美元，</t>
+  </si>
+  <si>
+    <t>[{'币种': 'GOOGL', '点位': 2.31}, {'币种': 'GOOGL', '点位': 2.85}, {'币种': 'GOOGL', '点位': 2.95}, {'币种': 'GOOGL', '点位': 9.11}]</t>
   </si>
   <si>
     <t>2026-07-23 22:25:35</t>
@@ -1353,6 +1566,9 @@
 #代币化股票月转账量一年增170倍 </t>
   </si>
   <si>
+    <t>[{'币种': 'NVDA', '点位': 50.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 15:11:34</t>
   </si>
   <si>
@@ -1368,12 +1584,18 @@
 目前段永平的钱准备往AI 上靠，不过还没想好做哪个标的</t>
   </si>
   <si>
+    <t>['MU', 'SPCX']</t>
+  </si>
+  <si>
     <t>2026-07-23 21:34:18</t>
   </si>
   <si>
     <t xml:space="preserve">美股开盘，道指跌 0.92%，标普 500 指数跌 1.12%，纳指跌 1.75%。
 特斯拉 (TSLA.O) 绩后开跌约 9%，因季度利润未达预期且自由现金流逾两年来首度转负。Alphabet(GOOG.O) 跌约 6%，此前上调财年资本支出预测，并警告现金流压力将持续。
 #交易之声：你的经验值得被听到 </t>
+  </si>
+  <si>
+    <t>['TSLA']</t>
   </si>
   <si>
     <t>2026-07-23 11:43:46</t>
@@ -1396,6 +1618,9 @@
 今天不急着猜消息最后怎么发展。
 我只看压力有没有继续传到盘面，再记住两个位置：65.5K和67K。 $BTC  
 #油价创六周高位，美伊冲突延续 </t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 65.8}, {'币种': 'BTC', '点位': 94.07}]</t>
   </si>
   <si>
     <t>2026-07-23 17:56:51</t>
@@ -1439,11 +1664,23 @@
 比特币这几天比较弱，如果稍微调整一下，不破6万，还会二次拉升目标6.8万~7.8万之间。如果你多单，可以止盈一半等待。</t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'LAB']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'ETH', '点位': 1350.0}]</t>
+  </si>
+  <si>
     <t>2026-07-22 19:26:26</t>
   </si>
   <si>
     <t>HYPE又遇“喊完单就跑”？和6月初Arthur Hayes一样？#交易之声：你的经验值得被听到 $HYPE 
 撰文：Shannon@金色财经 2026年5月初，与 Multicoin Capital 关联的三个钱包将共计196万枚 HYPE（当时价值约8206万美元）质押进 HyperCore，分散在三个独立地址，显示出精心设计的仓位管理意图。 6月25日，Multicoin 发布了对 Hyperliquid 迄今最系统的估值报告，在63美元的价格水平上，得出熊市109美元、基准319美元、牛市689美元的三档目标价，基准情景隐含约5倍上涨空间，报告核心论点是「HYPE 被严重低估」，并披露该仓位已是 Multicoin 最大的流动性仓位之一。 研报发布后约两周，7月22日，链上动作显示，与Multicoin关联的地址有39.557万枚 HYPE 转入Coinbase，5月初质押的196万枚 HYPE也被解质押并进入7天解质押等待序列，价值约1.2亿美元。 这就是这次操作的完整画面：质押八周→发布看多研报→两周后解质押+向 Coinbase 转账。 Multicoin 为何如此操作：</t>
+  </si>
+  <si>
+    <t>['COIN', 'CORE', 'HYPE']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'CORE', '点位': 63.0}, {'币种': 'CORE', '点位': 109.0}, {'币种': 'CORE', '点位': 319.0}, {'币种': 'CORE', '点位': 689.0}]</t>
   </si>
   <si>
     <t>2026-07-23 17:23:26</t>
@@ -1459,6 +1696,12 @@
 ✅ $VRT (Vertiv) — 在188美元附近关注
 ✅ $INTC (Intel) — 在86美元附近关注
 随着财报季的开始，人工智能、存储和半导体股票的势头已经回归。投资者正在密切关注最大科技公司的资本支出，这使得这些领域成为目前市场上最受关注的活跃区域之一。</t>
+  </si>
+  <si>
+    <t>['PLTR', 'MU', 'INTC', 'MRVL', 'NVDA']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'PLTR', '点位': 86.0}, {'币种': 'PLTR', '点位': 138.0}, {'币种': 'PLTR', '点位': 172.0}, {'币种': 'PLTR', '点位': 188.0}, {'币种': 'PLTR', '点位': 194.0}]</t>
   </si>
   <si>
     <t>2026-07-23 21:49:08</t>
@@ -1490,6 +1733,9 @@
 $BTC ，$ETH ，</t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'TRUMP']</t>
+  </si>
+  <si>
     <t>2026-07-23 11:18:04</t>
   </si>
   <si>
@@ -1497,6 +1743,9 @@
 营收1198亿超预期1169.3亿24%，云收入247.7亿、同比增加82%。资本开支指引从 1800亿—1900亿美元上调到1950亿—2050亿美元。
 股价跳水的根本原因在于二季度资本开支已经达到449亿美元，而经营现金流只有391亿美元，导致自由现金流转为 -58.6亿美元。
 还是那句话：谷歌的高收入意味着上下游厂商支出增加，高支出意味着上下游收入增加。海力士的反弹已经印证了这点，但能不能站稳还是要靠它自己。$GOOGL  #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
+  </si>
+  <si>
+    <t>['TSLA', 'GOOGL', 'SKHY']</t>
   </si>
   <si>
     <t>2026-07-23 15:06:35</t>
@@ -1521,6 +1770,9 @@
 目前来看，原油强势主要还是围绕地缘风险交易，短线继续关注88-90区域能否有效突破。如果突破站稳，市场可能继续打开上涨空间；如果冲高受阻，回踩确认支撑也是正常走势。
 交易上我更倾向顺势看待，不盲目追高，等待回踩关键位置再寻找机会。原油这种品种，消息驱动占比很高，控制仓位比判断方向更加重要。
 $BTC $ETH #油价创六周高位，美伊冲突延续 </t>
+  </si>
+  <si>
+    <t>[{'币种': 'CL', '点位': 67.0}, {'币种': 'CL', '点位': 80.0}, {'币种': 'CL', '点位': 88.0}, {'币种': 'CL', '点位': 90.0}]</t>
   </si>
   <si>
     <t>2026-07-23 21:22:03</t>
@@ -1554,6 +1806,9 @@
 对于BTC来说：短期不要忽视美股风险传导，真正的大机会，往往不是在市场最疯狂的时候出现，而是在一次流动性清洗之后。</t>
   </si>
   <si>
+    <t>[{'币种': 'BTC', '点位': 26000.0}, {'币种': 'BTC', '点位': 28000.0}, {'币种': 'BTC', '点位': 30000.0}, {'币种': 'BTC', '点位': 31000.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 20:21:25</t>
   </si>
   <si>
@@ -1575,6 +1830,12 @@
 $BTC 、$SKHYNIX $ETH </t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'SKHY']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'ETH', '点位': 7000.0}, {'币种': 'ETH', '点位': 8000.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 20:41:09</t>
   </si>
   <si>
@@ -1585,6 +1846,9 @@
 但现在油价确实也比较高了，也不适合追多，10年期美债收益率都要破4.7了，早就超过了此前川普的TACO点。
 当下美伊问题核心其实是缺乏退出机制问题，美伊任何一方根本没有无损的从冲突中退出路径。那么战争在最终结束前注定会有无数次博弈。而战争失败的结果注定需要有个足够分量的人来背——要么牺牲选情，要么牺牲内涵成员。或者最起码还是再大打一顿取得一些拿得出手的成果才能走。
 虽然AI概念股已经被砸了很多似乎刚刚有站稳迹象，但在持续高涨的油价之下，加息预期注定抬头。金银股饼都无法在通胀加息现金流恶化的大背景下独善其身。$CL   #油价创六周高位，美伊冲突延续 </t>
+  </si>
+  <si>
+    <t>['CL']</t>
   </si>
   <si>
     <t>2026-07-23 13:31:10</t>
@@ -1608,6 +1872,9 @@
 特斯拉最难的地方在于，汽车业务原本应该为Robotaxi、Optimus和芯片投入提供现金流，但汽车利润率已经先下来了，新业务又暂时没有接上。
 积极信号是，服务及其他收入增长50%至45.8亿美元，毛利率达到14.1%的历史高位；FSD付费客户增至148万，同比增长56%。但其中55%是一次性买断，真正的订阅用户占45%。Robotaxi虽然累计完成超过38万英里的无人监督行驶，公司却仍未披露单车收入、运营成本和回本周期。技术进展可以确认，商业模式还没法算账。
 两家公司都在重构商业模式，但所处阶段不同：谷歌已经开始用Cloud和AI赚到真金白银，接下来验证资本回报；特斯拉拿出了FSD渗透率和Robotaxi里程，却还没有形成足以覆盖汽车利润下降的新利润池。说得直接一点：谷歌的问题是投这么多钱，最后能赚多少；特斯拉的问题是新业务什么时候才能真正赚钱。</t>
+  </si>
+  <si>
+    <t>[{'币种': 'SPCX', '点位': 282.0}, {'币种': 'SPCX', '点位': 5140.0}]</t>
   </si>
   <si>
     <t>2026-07-23 14:11:45</t>
@@ -1791,6 +2058,12 @@
 （整理自 Serenity 观点与公开材料，仅供学习，不构成投资建议）</t>
   </si>
   <si>
+    <t>['SPCX', 'GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'SPCX', '点位': 2.85}]</t>
+  </si>
+  <si>
     <t>2026-07-23 22:53:14</t>
   </si>
   <si>
@@ -1820,6 +2093,9 @@
 同时，$SOL、$XRP 等高市值公链和支付类资产，也可能受到合规预期提升的影响。
 不过，短期行情仍取决于最终投票结果。距离休会窗口越来越近，政治博弈仍可能带来反复。
 监管清晰化是长期利好，但市场不会只交易预期。真正的行情启动，还需要看到法案最终通过以及资金端的实际反馈。$BTC $LAB </t>
+  </si>
+  <si>
+    <t>['BTC', 'ETH', 'SOL', 'XRP', 'LAB']</t>
   </si>
   <si>
     <t>2026-07-23 15:48:07</t>
@@ -1842,6 +2118,9 @@
 行业急得像热锅上的蚂蚁，Coinbase、Blockchain Association全在催。但政治这东西，从来不care你的 urgency。
 盯着下周参议院动向吧！
 谈崩了就继续熊，谈成了或许能冲一波65000。否则，继续在泥潭里打滚。$BTC $ETH 韭菜们，系好安全带，这出戏还tm早着呢！</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 12.0}, {'币种': 'BTC', '点位': 14.0}, {'币种': 'BTC', '点位': 66.0}]</t>
   </si>
   <si>
     <t>2026-07-23 17:42:06</t>
@@ -1955,6 +2234,9 @@
 目前美元持续走强，对风险资产是一种潜在压制，这可能会刺激美股继续震荡回调走势！#财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
   </si>
   <si>
+    <t>[{'币种': 'INTC', '点位': 1.7}]</t>
+  </si>
+  <si>
     <t>2026-07-23 17:55:13</t>
   </si>
   <si>
@@ -1993,6 +2275,9 @@
 两边都是赌场，杠杆越大死得越快。自己掂量，别当冤大头。​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​</t>
   </si>
   <si>
+    <t>['COIN', 'BTC', 'ETH', 'SKHY']</t>
+  </si>
+  <si>
     <t>2026-07-23 20:47:00</t>
   </si>
   <si>
@@ -2021,6 +2306,9 @@
 #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
   </si>
   <si>
+    <t>[{'币种': 'TSLA', '点位': 309.0}, {'币种': 'TSLA', '点位': 319.0}, {'币种': 'TSLA', '点位': 333.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 19:23:26</t>
   </si>
   <si>
@@ -2056,6 +2344,9 @@
 如果你误以为买入代币，等于持有正规股票、享有全部股东权益，那趁早清醒。监管利剑一直悬在头顶，这类产品甚至不对美国本土用户开放，长期发展天花板肉眼可见。</t>
   </si>
   <si>
+    <t>['SNDK', 'MU', 'TSLA', 'NVDA', 'GOOGL']</t>
+  </si>
+  <si>
     <t>2026-07-23 20:27:19</t>
   </si>
   <si>
@@ -2066,6 +2357,12 @@
 记住，油价涨出的避险买盘，和降息预期推出来的牛市，是两码事。
 如果原油CL来到了88-95-110区间可以分批布局空单，知音80-70-60附近，低倍长期持有错不了！
 关注法老，财富不迷路！$BTC $ETH $LAB #油价创六周高位，美伊冲突延续 </t>
+  </si>
+  <si>
+    <t>['BTC', 'ETH', 'LAB', 'CL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'LAB', '点位': 60.0}, {'币种': 'LAB', '点位': 70.0}, {'币种': 'LAB', '点位': 80.0}, {'币种': 'LAB', '点位': 84.0}, {'币种': 'LAB', '点位': 88.0}]</t>
   </si>
   <si>
     <t>2026-07-23 11:53:47</t>
@@ -2092,6 +2389,9 @@
 原因很简单，它已经证明 AI 可以持续贡献收入，Google Cloud、Gemini、搜索广告形成了比较完整的商业闭环；而特斯拉未来最大的价值依然建立在 Robotaxi 和 Optimus 能否真正兑现，这里面还有不少变量。
 市场最终奖励的，从来不是投入最多的公司，而是最先把 AI 变成现金流的公司。
 #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
+  </si>
+  <si>
+    <t>[{'币种': 'TSLA', '点位': 280.0}]</t>
   </si>
   <si>
     <t>2026-07-23 14:09:40</t>
@@ -2131,6 +2431,9 @@
 谷歌在AI赛道上已经开始收割，特斯拉还在裸奔赌明天！本大王直接All in谷歌，特斯拉爱谁谁去，爱信不信！ ​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​​ </t>
   </si>
   <si>
+    <t>[{'币种': 'TSLA', '点位': 2.0}, {'币种': 'TSLA', '点位': 9.11}, {'币种': 'TSLA', '点位': 449.0}, {'币种': 'TSLA', '点位': 1950.0}, {'币种': 'TSLA', '点位': 2050.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 08:32:57</t>
   </si>
   <si>
@@ -2161,6 +2464,9 @@
 并且现在表决前景很不利：时间紧，票数不够，双方肯定还要继续拉扯一段时间。
 我的观点：这就是一场分赃不均的政治表演：​ 共和党拿道德条款当挡箭牌，告诉选民“我们连总统都管住了”；民主党嫌力度不够，要更严格的利益冲突限制。两边都在演戏，真正受伤的是散户。
 说不定等$TRUMP币跌了97%，$WLFI 跌了99%，特朗普家族赚的盆满钵满，韭菜被割完了，监管才姗姗来迟。</t>
+  </si>
+  <si>
+    <t>['BTC', 'ETH', 'TRUMP', 'WLFI']</t>
   </si>
   <si>
     <t>2026-07-23 16:14:05</t>
@@ -2381,6 +2687,9 @@
 #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
   </si>
   <si>
+    <t>['MU', 'TSLA', 'GOOGL', 'SKHY']</t>
+  </si>
+  <si>
     <t>2026-07-23 17:14:01</t>
   </si>
   <si>
@@ -2520,6 +2829,9 @@
 #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ $XGOOGL $XTSLA </t>
   </si>
   <si>
+    <t>[{'币种': 'BTC', '点位': 11509.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 18:55:29</t>
   </si>
   <si>
@@ -2603,6 +2915,12 @@
 4. 短期波动区分清楚：存储板块韩股下跌属于杠杆资金筹码踩踏，和产业供需无关，去杠杆接近尾声，海内外存储产业链同步具备修复空间。</t>
   </si>
   <si>
+    <t>['SKHY', 'AVGO', 'MU', 'TSM', 'NVDA']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'SKHY', '点位': 1.0}, {'币种': 'AVGO', '点位': 1250.0}, {'币种': 'AVGO', '点位': 1450.0}, {'币种': 'AVGO', '点位': 1950.0}, {'币种': 'AVGO', '点位': 2050.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 21:01:13</t>
   </si>
   <si>
@@ -2631,6 +2949,9 @@
 其实一开始就得到了   $BTC  $ETH  #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ </t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'GOOGL', 'TSLA']</t>
+  </si>
+  <si>
     <t>2026-07-23 13:27:06</t>
   </si>
   <si>
@@ -2657,6 +2978,9 @@
 所以我的选择是：谷歌打底，特斯拉观察。
 如果你有闲钱、能扛波动、愿意赌一个十年后的颠覆性故事，特斯拉值得配置一部分。但如果只能选一个长期拿着，我选谷歌——它在AI时代的护城河是可计算的，而特斯拉的护城河目前还是可想象的。
 投资里，可计算的确定性，永远比可想象的赔率更值钱</t>
+  </si>
+  <si>
+    <t>['MU', 'TSLA', 'GOOGL']</t>
   </si>
   <si>
     <t>2026-07-23 23:10:04</t>
@@ -2688,6 +3012,12 @@
 英特尔、IBM紧接着披露业绩，后续还有微软、Meta、苹果、亚马逊轮番登场。</t>
   </si>
   <si>
+    <t>['SNDK', 'MU', 'TSLA', 'INTC', 'SKHY', 'GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'SNDK', '点位': 1000.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 23:24:20</t>
   </si>
   <si>
@@ -2721,6 +3051,9 @@
 近期一直强调，空单持有不必慌张，上方已见顶，不必过度追涨，事实证明锋哥再次精准预判拐点。
 日内空单已离场，长线布局还在持有。
 $BTC ethereum:native</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 44.0}, {'币种': 'BTC', '点位': 1100.0}]</t>
   </si>
   <si>
     <t>2026-07-23 21:04:46</t>
@@ -2769,6 +3102,12 @@
  这也解释了为什么出售流程走了一年多无人接手。发明权、品牌、技术栈和牌照都还在，唯独流动性不在，而买家真正要买的或许只是后者。</t>
   </si>
   <si>
+    <t>['COIN', 'BTC', 'BMEX']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'COIN', '点位': 1.29}, {'币种': 'COIN', '点位': 2016.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 21:28:01</t>
   </si>
   <si>
@@ -2784,6 +3123,9 @@
 耐心是我的策略——等待确认信号，而非冲动交易。</t>
   </si>
   <si>
+    <t>[{'币种': 'BTC', '点位': 64.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 21:23:51</t>
   </si>
   <si>
@@ -2797,6 +3139,9 @@
 逻辑复盘：ETH这两天从1,950上方持续回落，1,900-1,920是短期支撑带，上方1,930-1,950是密集压力区。两单都卡在压力位做空，回踩支撑附近止盈，顺势而为比赌方向靠谱得多。
 总结：方向对了，50倍杠杆是朋友，方向错了就是魔鬼。盈利的时候别贪，落袋为安！🍖
 #ETH #以太坊 #合约交易 #精准狙击 #落袋为安</t>
+  </si>
+  <si>
+    <t>[{'币种': 'ETH', '点位': 915.4}, {'币种': 'ETH', '点位': 924.01}, {'币种': 'ETH', '点位': 931.34}, {'币种': 'ETH', '点位': 940.59}, {'币种': 'ETH', '点位': 1900.0}]</t>
   </si>
   <si>
     <t>2026-07-23 23:24:01</t>
@@ -2829,6 +3174,9 @@
 它既是以太坊主网的Gas资产，也是PoS网络的质押资产，同时还是大量DeFi、稳定币和Layer 2生态的重要结算资产。链上活动越活跃，对ETH作为手续费、抵押品和安全资产的需求就越值得关注。
 当然，ETH并没有固定供应上限。它同时存在质押发行与手续费销毁，最终是通胀还是通缩，要看网络使用情况，不能简单理解成“必然通缩”。
 所以我觉得，ETH接下来的重点不只是能否重新站上2000美元，而是机构质押需求、Glamsterdam升级和链上活跃度能否形成共振。</t>
+  </si>
+  <si>
+    <t>[{'币种': 'ETH', '点位': 1930.0}, {'币种': 'ETH', '点位': 2000.0}]</t>
   </si>
   <si>
     <t>2026-07-23 23:21:20</t>
@@ -2920,6 +3268,9 @@
 2. 第二支撑：65000整数关口
 3. 强支撑：64000~64300美元，本轮反弹启动平台
 今天还是看美股开市，大概率还是低开然后慢慢的开始反弹，先给比特币来一针，骗空头入场，然后持续缓慢上升。#油价创六周高位，美伊冲突延续 </t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 64300.0}, {'币种': 'BTC', '点位': 65300.0}, {'币种': 'BTC', '点位': 66000.0}, {'币种': 'BTC', '点位': 66800.0}, {'币种': 'BTC', '点位': 66920.0}]</t>
   </si>
   <si>
     <t>2026-07-23 23:23:17</t>
@@ -2994,6 +3345,9 @@
 #KOSPI破7000，韩国加密交易量降89% </t>
   </si>
   <si>
+    <t>[{'币种': 'SKHY', '点位': 135.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 23:24:05</t>
   </si>
   <si>
@@ -3001,6 +3355,9 @@
   </si>
   <si>
     <t>ETH以太坊整体趋势走弱，短线只是超跌小幅反弹，并非反转行情。下方关键支撑在1882，破位还会继续下探。稳健暂时观望，不要抄底做多；反弹至1910附近可顺势开空，严格带好止损。</t>
+  </si>
+  <si>
+    <t>[{'币种': 'ETH', '点位': 1910.0}]</t>
   </si>
   <si>
     <t>2026-07-23 21:20:57</t>
@@ -3029,6 +3386,9 @@
 #MagnificentSeven #美股七姐妹 #AI</t>
   </si>
   <si>
+    <t>[{'币种': 'NVDA', '点位': 1950.0}, {'币种': 'NVDA', '点位': 2050.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 23:24:35</t>
   </si>
   <si>
@@ -3047,6 +3407,9 @@
 这就是我们昨天在 $66K 上方做空的真正原因。</t>
   </si>
   <si>
+    <t>[{'币种': 'BTC', '点位': 66.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 23:24:55</t>
   </si>
   <si>
@@ -3054,6 +3417,9 @@
 市场永远不会亏待有准备的人。
 下一轮机会来的时候，希望你已经不是那个追涨杀跌的小白。
 而是那个能冷静吃肉的人。$BTC $ETH $SOL </t>
+  </si>
+  <si>
+    <t>['BTC', 'ETH', 'SOL']</t>
   </si>
   <si>
     <t>2026-07-23 23:24:45</t>
@@ -3088,6 +3454,9 @@
 - 带话题 #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ ，即可创作
 🎁 参与创作：瓜分 70000U 美股包赔券 / 空投券，0 风险开启美股投资 
 ⭐ 优质内容：流量加权曝光，官方账号转发 + 收录进官方栏目</t>
+  </si>
+  <si>
+    <t>[{'币种': 'TSLA', '点位': 70000.0}]</t>
   </si>
   <si>
     <t>2026-07-23 16:40:28</t>
@@ -3136,6 +3505,12 @@
 3. 美股科技股财报季的整体表现，若多家龙头业绩不及预期，美股会带动全市场继续回调。$SNDK </t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'GOOGL', 'SNDK']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 1.0}, {'币种': 'BTC', '点位': 7.0}, {'币种': 'BTC', '点位': 90.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 23:23:29</t>
   </si>
   <si>
@@ -3146,6 +3521,9 @@
 $SPCX 、$SNDK 这两只票上演群魔乱舞，不少追高的人深套其中，反复被来回收割。
 喧嚣到这种地步，我倾向认定这是最后的狂欢，属于这一波行情的最后一舞，敬请期待接下来的变局。
 乱世行情别盲目重仓，耐心等待信号，不要被短期波动牵着情绪走。</t>
+  </si>
+  <si>
+    <t>['SPCX', 'SNDK']</t>
   </si>
   <si>
     <t>2026-07-23 18:58:26</t>
@@ -3202,6 +3580,9 @@
     <t>兄弟们，ETH又在2000美元门口玩起了"狼来了"。 今日ETH最高摸到1941美元，现报1901美元，从6月低点1514美元反弹了27%——但到了1955附近就反复被锤，2000美元的心理关口就是捅不破。 凭什么？三把刀悬在头顶—— 第一刀：油价狂飙，通胀阴魂不散 中东局势持续升温，WTI原油连续第五天上涨，突破90美元/桶。特朗普和伊朗互放狠话，霍尔木兹海峡仍是火药桶。 油价涨意味着什么？通胀压不住。美联储本来憋着要降息，现在通胀一抬头，9月加息概率已经从68%飙到79%。风险资产？先跌为敬。 第二刀：BitMEX计划停业，老牌交易所谢幕 BitMEX计划停止运营的消息冲击市场情绪。作为衍生品交易的鼻祖级平台，它的谢幕让市场多了一丝寒意——连老牌玩家都撑不住了，这轮熊市底部到底在哪？ 第三刀：2000美元成了"鬼门关" ETH从1514到1941，技术上确实反弹了27%，但问题在于——量能跟不上，抛压扛不住。每次靠近1955就被砸下来，说明这个位置套牢盘太重，多头没信心硬冲。 更让人担心的是，如果2000美元久攻不下，多头耐心耗尽，会不会再次回踩？毕竟从底部起来已经涨了400多刀，</t>
   </si>
   <si>
+    <t>[{'币种': 'CL', '点位': 90.0}, {'币种': 'CL', '点位': 1514.0}, {'币种': 'CL', '点位': 1901.0}, {'币种': 'CL', '点位': 1941.0}, {'币种': 'CL', '点位': 1955.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 17:43:37</t>
   </si>
   <si>
@@ -3230,6 +3611,12 @@
 不作为任何投资建议DYOR</t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'MU', 'TSLA', 'MRVL', 'SKHY']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 2.0}, {'币种': 'BTC', '点位': 3.0}, {'币种': 'ETH', '点位': 1930.0}, {'币种': 'ETH', '点位': 2030.0}, {'币种': 'ETH', '点位': 2080.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 21:21:51</t>
   </si>
   <si>
@@ -3243,6 +3630,9 @@
 当前流通市值仅 $2965 万，但总供应量 21 亿中已有 59.27% 进入流通。低流通市值意味着少量资金即可引发价格弹性，而高流通率则降低了后续解锁抛压的不确定性——这是很多新币不具备的安全垫。
 链上行为与价格的背离
 （此处可插入 Dune/OKX 链上数据截图）尽管价格横盘，但 CORE 近 30 天活跃地址数环比上升 XX%，大额转账频次增加。这种“价平量增”往往是主力吸筹的典型特征，比单纯看 K 线更可靠。 </t>
+  </si>
+  <si>
+    <t>['CORE']</t>
   </si>
   <si>
     <t>2026-07-23 21:24:08</t>
@@ -3286,6 +3676,9 @@
 $ETH $BTC $SOL #以太坊 #监管回暖 #机构回流</t>
   </si>
   <si>
+    <t>[{'币种': 'ETH', '点位': 1800.0}, {'币种': 'ETH', '点位': 1950.0}, {'币种': 'ETH', '点位': 1960.0}, {'币种': 'ETH', '点位': 2000.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 21:11:41</t>
   </si>
   <si>
@@ -3337,6 +3730,9 @@
   </si>
   <si>
     <t>链上数据7月前10个人巨鲸累计加仓$SATS 超100万U美金</t>
+  </si>
+  <si>
+    <t>['SATS']</t>
   </si>
   <si>
     <t>2026-07-23 21:21:06</t>
@@ -3368,6 +3764,12 @@
 播客链接放评论区👇</t>
   </si>
   <si>
+    <t>['MU']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'MU', '点位': 5.0}, {'币种': 'MU', '点位': 7.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 21:20:53</t>
   </si>
   <si>
@@ -3385,6 +3787,9 @@
   </si>
   <si>
     <t>$KAITO 狗哥你要能拉到2刀我就认输😂</t>
+  </si>
+  <si>
+    <t>[{'币种': 'KAITO', '点位': 2.0}]</t>
   </si>
   <si>
     <t>2026-07-23 19:55:38</t>
@@ -3411,6 +3816,12 @@
 巨鲸实盘认领，1.8 亿美元做空 BTC：大户「先定 10 个大目标」确认币安实盘账户「Jason leo133」为其本人。目前持有 2,741 枚 BTC 空单（均价 $65,970），总仓位约 $1.8 亿，目前微亏 40 万美元</t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'COIN', 'TSLA', 'HYPE', 'GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'BTC', '点位': 65970.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 19:21:45</t>
   </si>
   <si>
@@ -3439,6 +3850,9 @@
 #KOSPI破7000，韩国加密交易量降89% #交易之声：你的经验值得被听到 #AFX跨链桥被盗2415万USDC </t>
   </si>
   <si>
+    <t>[{'币种': 'ETH', '点位': 700.0}, {'币种': 'ETH', '点位': 1000.0}, {'币种': 'ETH', '点位': 1620.0}, {'币种': 'ETH', '点位': 1680.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 21:25:53</t>
   </si>
   <si>
@@ -3455,6 +3869,9 @@
   </si>
   <si>
     <t xml:space="preserve">$SPCX  已跌破 120 美元关键支撑，目前正在 110 美元附近寻找新的平衡区间。 值得关注的是，目前约 56% 的自由流通股已被借出用于做空。如此高的做空比例，意味着市场空头情绪已经较为集中，也为后续行情埋下了一定的不确定性。 就我个人而言，如果价格已经来到 110 美元附近，再继续追空的风险收益比并不高；若后续有效跌破 110反而有顺势做空的价值。 另外，北京时间凌晨 6:30 将迎来新一轮发射，这也可能成为短期情绪的重要催化剂。 《易经》中有一卦名为 泽水困——困境之中，保持德行，不轻举妄动，困极则通。 易经泽水困卦对应到我们的交易纪律，仓位就是最大的德行，无论看多还是看空，当前最重要的不是预测方向，而是控制仓位。 健康的仓位，才有机会等到“易”的出现。 最后，祝道友开仓即赚，万事ok！ #交易之声：你的经验值得被听到  #代币化股票月转账量一年增170倍  #新手必看：这里有你需要的一切 </t>
+  </si>
+  <si>
+    <t>[{'币种': 'SPCX', '点位': 110.0}, {'币种': 'SPCX', '点位': 120.0}, {'币种': 'SPCX', '点位': 170.0}]</t>
   </si>
   <si>
     <t>2026-07-23 21:26:04</t>
@@ -3498,6 +3915,12 @@
 #油价创六周高位，美伊冲突延续 </t>
   </si>
   <si>
+    <t>['BTC', 'SNDK', 'TSLA', 'LAB', 'GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'SNDK', '点位': 1300.0}, {'币种': 'SNDK', '点位': 1672.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 23:22:00</t>
   </si>
   <si>
@@ -3548,6 +3971,9 @@
 这也是我最近一直提醒自己的一句话。</t>
   </si>
   <si>
+    <t>['NVDA', 'SKHY', 'GOOGL', 'TSLA']</t>
+  </si>
+  <si>
     <t>2026-07-23 21:25:52</t>
   </si>
   <si>
@@ -3570,6 +3996,9 @@
 数据截至 2026-07-23 21:20，以上仅为行情分析，不构成投资建议。</t>
   </si>
   <si>
+    <t>[{'币种': 'ETH', '点位': 7.0}, {'币种': 'ETH', '点位': 20.0}, {'币种': 'ETH', '点位': 21.0}, {'币种': 'ETH', '点位': 23.0}, {'币种': 'ETH', '点位': 50.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 21:25:28</t>
   </si>
   <si>
@@ -3590,6 +4019,12 @@
 坐等利润奔跑，让子弹飞一会儿📉 $BTC $ETH $LAB #财报观察员：谁能看懂谷歌和特斯拉这次的真实答卷？ #参议院发布CLARITY新文本，最快下周表决 #油价创六周高位，美伊冲突延续 </t>
   </si>
   <si>
+    <t>['BTC', 'ETH', 'TSLA', 'LAB', 'GOOGL']</t>
+  </si>
+  <si>
+    <t>[{'币种': 'ETH', '点位': 4676.0}, {'币种': 'ETH', '点位': 8621.0}, {'币种': 'BTC', '点位': 66809.0}]</t>
+  </si>
+  <si>
     <t>2026-07-23 23:24:26</t>
   </si>
   <si>
@@ -3606,6 +4041,9 @@
   </si>
   <si>
     <t>早上我说闪迪要暴跌，你跟上了吗？ $SNDK 全仓 20x 开仓价格 1598 现价已经来到 1560 浮盈 +14,053U 收益率 +48.83% 早上我说闪迪今天明天该跌了。 自己还加仓空了一手。 分析了闪迪行情，压力位在1620附近。 结果闪迪今天洗了一下午。 不断诱多，涨到1636附近。 不过我没慌。 结果晚上直接开砸。 1636跌到1560。 76个点的跌幅。 直接从浮亏直接干到浮盈一万四。 加仓加到点上了。 自己赚钱虽然很开心。 但是今天还带了看我帖子的粉丝赚钱了。 这才是最让我开心的。 感觉自己的内容非常有意义。 现在这个位置跟上的宝宝们可以先考虑止盈一部分。 剩下的继续拿着，行情还没有走完。</t>
+  </si>
+  <si>
+    <t>[{'币种': 'SNDK', '点位': 1598.0}, {'币种': 'SNDK', '点位': 1620.0}, {'币种': 'SNDK', '点位': 1636.0}, {'币种': 'SNDK', '点位': 14053.0}]</t>
   </si>
   <si>
     <t>2026-07-23 21:24:13</t>
@@ -3672,6 +4110,9 @@
   </si>
   <si>
     <t>晚间急报：均线结构（VWMA成交量加权均线） VWMA5：1571.01 VWMA10：1584.75 VWMA20：1598.44 现价 1560.76 已经全部跌破三条量价均线 短期趋势由震荡转为偏弱，均线由支撑转变为压力。 2. 关键价位（图内标注） 👇支撑：1515.93（近期重要低点支撑区间） 👇压力：1606.73 3．中间短期压力带：1571 ~ 1584（均线承压区） 过去一段时间行情在1520 ~ 1658区间宽幅震荡，多次反弹触碰1640上方承压回落； 当前这一波下跌，是震荡上沿多次冲击失败后的一轮下行。 4.过去一段时间行情在1520 ~ 1658区间宽幅震荡，多次反弹触碰1640上方承压回落； 当前这一波下跌，是震荡上沿多次冲击失败后的一轮下行。 📊总结 短期趋势偏弱，指标超跌存在修复反弹需求，整体处于【震荡破位初期】。 重点观察两个核心区间： 压力区：1570 — 1585 支撑区：1516 反弹遇阻则偏空；站稳压力才能转强；跌破支撑开启新一轮下跌。$SNDK #闪迪#代币化股票月转账量一年增170倍 #交易之声：你的经验值得被听到 @天才交易员绿毛 @</t>
+  </si>
+  <si>
+    <t>[{'币种': 'SNDK', '点位': 3.0}, {'币种': 'SNDK', '点位': 1606.73}, {'币种': 'SNDK', '点位': 1640.0}]</t>
   </si>
   <si>
     <t>2026-07-23 23:13:11</t>
@@ -3715,6 +4156,9 @@
   </si>
   <si>
     <t xml:space="preserve">一个数据看得我有点沉默。CryptoQuant 说，持仓不超过 155 天的短线玩家，已经连续九个月处在亏损兑现的状态。九个月。这不是回调，这是漫长的被收割。 他们的持仓成本大概在 68,800 美金，现在 BTC 想站稳 65,000 上方，他们还在以大概 4% 的亏损幅度割肉。也就是说，过去大半年里，每一次反弹都是给短线选手一个"少亏点跑"的机会，然后继续跌。 我太懂这种感觉了。2021 年那一波，我也是那个"解套就跑、跑了还跌"的人。短线玩家的命门不是看不准，是成本线被套住后，每一笔卖都是亏着卖，越卖越确认自己错了。 现在 65,000 这个位置很关键。站稳了，这批人才能喘口气；站不稳，又是一轮被动止损。 我好奇一件事：在看的各位，你现在是那批被套九个月的，还是早就空仓看戏的？评论区说说你成本线在哪，咱互相安慰一下。 #Bitcoin #短线 #持仓成本 #65K#交易之声：你的经验值得被听到 </t>
+  </si>
+  <si>
+    <t>[{'币种': 'COIN', '点位': 65.0}, {'币种': 'BTC', '点位': 65000.0}, {'币种': 'BTC', '点位': 68800.0}]</t>
   </si>
   <si>
     <t>2026-07-23 21:22:46</t>
@@ -3746,6 +4190,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -4200,153 +4645,155 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4693,2353 +5140,3734 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C213"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:F213"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="26.25" customWidth="1"/>
+    <col min="3" max="3" width="117.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" t="s">
+        <v>125</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" t="s">
+        <v>135</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>146</v>
+      </c>
+      <c r="B40" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" t="s">
+        <v>148</v>
+      </c>
+      <c r="D40" t="s">
+        <v>149</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41" t="s">
+        <v>152</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C42" t="s">
+        <v>155</v>
+      </c>
+      <c r="D42" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>157</v>
+      </c>
+      <c r="B43" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="C43" t="s">
+        <v>158</v>
+      </c>
+      <c r="D43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>161</v>
+      </c>
+      <c r="B44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" t="s">
+        <v>162</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>163</v>
+      </c>
+      <c r="B45" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" t="s">
+        <v>166</v>
+      </c>
+      <c r="E45" t="s">
+        <v>167</v>
+      </c>
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>168</v>
+      </c>
+      <c r="B46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" t="s">
+        <v>169</v>
+      </c>
+      <c r="D46" t="s">
+        <v>83</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B47" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>173</v>
+      </c>
+      <c r="B48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" t="s">
+        <v>87</v>
+      </c>
+      <c r="E48" t="s">
+        <v>175</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>176</v>
+      </c>
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" t="s">
+        <v>177</v>
+      </c>
+      <c r="D49" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E49" t="s">
+        <v>178</v>
+      </c>
+      <c r="F49" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>179</v>
+      </c>
+      <c r="B50" t="s">
+        <v>180</v>
+      </c>
+      <c r="C50" t="s">
+        <v>181</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" t="s">
+        <v>182</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>183</v>
+      </c>
+      <c r="B51" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" t="s">
+        <v>115</v>
+      </c>
+      <c r="E51" t="s">
+        <v>186</v>
+      </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
+        <v>188</v>
+      </c>
+      <c r="D52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>189</v>
+      </c>
+      <c r="B53" t="s">
+        <v>190</v>
+      </c>
+      <c r="C53" t="s">
+        <v>191</v>
+      </c>
+      <c r="D53" t="s">
+        <v>192</v>
+      </c>
+      <c r="E53" t="s">
+        <v>193</v>
+      </c>
+      <c r="F53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>194</v>
+      </c>
+      <c r="B54" t="s">
+        <v>195</v>
+      </c>
+      <c r="C54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" t="s">
+        <v>197</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>198</v>
+      </c>
+      <c r="B55" t="s">
+        <v>199</v>
+      </c>
+      <c r="C55" t="s">
+        <v>200</v>
+      </c>
+      <c r="D55" t="s">
+        <v>83</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>201</v>
+      </c>
+      <c r="B56" t="s">
+        <v>202</v>
+      </c>
+      <c r="C56" t="s">
+        <v>203</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>204</v>
+      </c>
+      <c r="B57" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" t="s">
+        <v>206</v>
+      </c>
+      <c r="D57" t="s">
+        <v>207</v>
+      </c>
+      <c r="E57" t="s">
+        <v>208</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>209</v>
+      </c>
+      <c r="B58" t="s">
+        <v>210</v>
+      </c>
+      <c r="C58" t="s">
+        <v>211</v>
+      </c>
+      <c r="D58" t="s">
+        <v>212</v>
+      </c>
+      <c r="E58" t="s">
+        <v>213</v>
+      </c>
+      <c r="F58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>214</v>
+      </c>
+      <c r="B59" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" t="s">
+        <v>215</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>216</v>
+      </c>
+      <c r="B60" t="s">
+        <v>199</v>
+      </c>
+      <c r="C60" t="s">
+        <v>217</v>
+      </c>
+      <c r="D60" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" t="s">
+        <v>220</v>
+      </c>
+      <c r="D61" t="s">
+        <v>221</v>
+      </c>
+      <c r="E61" t="s">
+        <v>222</v>
+      </c>
+      <c r="F61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>223</v>
+      </c>
+      <c r="B62" t="s">
+        <v>113</v>
+      </c>
+      <c r="C62" t="s">
+        <v>224</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>225</v>
+      </c>
+      <c r="B63" t="s">
+        <v>226</v>
+      </c>
+      <c r="C63" t="s">
+        <v>227</v>
+      </c>
+      <c r="D63" t="s">
+        <v>228</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>229</v>
+      </c>
+      <c r="B64" t="s">
+        <v>230</v>
+      </c>
+      <c r="C64" t="s">
+        <v>231</v>
+      </c>
+      <c r="D64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>232</v>
+      </c>
+      <c r="B65" t="s">
+        <v>233</v>
+      </c>
+      <c r="C65" t="s">
+        <v>234</v>
+      </c>
+      <c r="D65" t="s">
+        <v>40</v>
+      </c>
+      <c r="E65" t="s">
+        <v>235</v>
+      </c>
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>236</v>
+      </c>
+      <c r="B66" t="s">
+        <v>237</v>
+      </c>
+      <c r="C66" t="s">
+        <v>238</v>
+      </c>
+      <c r="F66" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>239</v>
+      </c>
+      <c r="B67" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" t="s">
+        <v>240</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>241</v>
+      </c>
+      <c r="B68" t="s">
+        <v>226</v>
+      </c>
+      <c r="C68" t="s">
+        <v>242</v>
+      </c>
+      <c r="D68" t="s">
+        <v>166</v>
+      </c>
+      <c r="E68" t="s">
+        <v>243</v>
+      </c>
+      <c r="F68" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>244</v>
+      </c>
+      <c r="B69" t="s">
+        <v>245</v>
+      </c>
+      <c r="C69" t="s">
+        <v>246</v>
+      </c>
+      <c r="D69" t="s">
+        <v>40</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
+        <v>247</v>
+      </c>
+      <c r="B70" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" t="s">
+        <v>248</v>
+      </c>
+      <c r="D70" t="s">
+        <v>249</v>
+      </c>
+      <c r="E70" t="s">
+        <v>250</v>
+      </c>
+      <c r="F70" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
+        <v>251</v>
+      </c>
+      <c r="B71" t="s">
+        <v>252</v>
+      </c>
+      <c r="C71" t="s">
+        <v>253</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
+        <v>254</v>
+      </c>
+      <c r="B72" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" t="s">
+        <v>255</v>
+      </c>
+      <c r="D72" t="s">
+        <v>83</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>256</v>
+      </c>
+      <c r="B73" t="s">
+        <v>257</v>
+      </c>
+      <c r="C73" t="s">
+        <v>258</v>
+      </c>
+      <c r="D73" t="s">
+        <v>228</v>
+      </c>
+      <c r="E73" t="s">
+        <v>259</v>
+      </c>
+      <c r="F73" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
+        <v>260</v>
+      </c>
+      <c r="B74" t="s">
+        <v>261</v>
+      </c>
+      <c r="C74" t="s">
+        <v>262</v>
+      </c>
+      <c r="F74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
+        <v>263</v>
+      </c>
+      <c r="B75" t="s">
+        <v>76</v>
+      </c>
+      <c r="C75" t="s">
+        <v>264</v>
+      </c>
+      <c r="D75" t="s">
+        <v>265</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>266</v>
+      </c>
+      <c r="B76" t="s">
+        <v>267</v>
+      </c>
+      <c r="C76" t="s">
+        <v>268</v>
+      </c>
+      <c r="D76" t="s">
+        <v>62</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>269</v>
+      </c>
+      <c r="B77" t="s">
+        <v>120</v>
+      </c>
+      <c r="C77" t="s">
+        <v>270</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
+        <v>271</v>
+      </c>
+      <c r="B78" t="s">
+        <v>272</v>
+      </c>
+      <c r="C78" t="s">
+        <v>273</v>
+      </c>
+      <c r="D78" t="s">
+        <v>274</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>275</v>
+      </c>
+      <c r="B79" t="s">
+        <v>276</v>
+      </c>
+      <c r="C79" t="s">
+        <v>277</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
+        <v>278</v>
+      </c>
+      <c r="B80" t="s">
+        <v>279</v>
+      </c>
+      <c r="C80" t="s">
+        <v>280</v>
+      </c>
+      <c r="D80" t="s">
+        <v>281</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>282</v>
+      </c>
+      <c r="B81" t="s">
+        <v>113</v>
+      </c>
+      <c r="C81" t="s">
+        <v>283</v>
+      </c>
+      <c r="F81" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>284</v>
+      </c>
+      <c r="B82" t="s">
+        <v>50</v>
+      </c>
+      <c r="C82" t="s">
+        <v>285</v>
+      </c>
+      <c r="D82" t="s">
+        <v>286</v>
+      </c>
+      <c r="F82" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>287</v>
+      </c>
+      <c r="B83" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" t="s">
+        <v>288</v>
+      </c>
+      <c r="D83" t="s">
+        <v>83</v>
+      </c>
+      <c r="E83" t="s">
+        <v>289</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>290</v>
+      </c>
+      <c r="B84" t="s">
+        <v>276</v>
+      </c>
+      <c r="C84" t="s">
+        <v>291</v>
+      </c>
+      <c r="D84" t="s">
+        <v>144</v>
+      </c>
+      <c r="E84" t="s">
+        <v>145</v>
+      </c>
+      <c r="F84" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
+        <v>292</v>
+      </c>
+      <c r="B85" t="s">
+        <v>293</v>
+      </c>
+      <c r="C85" t="s">
+        <v>294</v>
+      </c>
+      <c r="D85" t="s">
+        <v>22</v>
+      </c>
+      <c r="E85" t="s">
+        <v>295</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>296</v>
+      </c>
+      <c r="B86" t="s">
+        <v>297</v>
+      </c>
+      <c r="C86" t="s">
+        <v>298</v>
+      </c>
+      <c r="D86" t="s">
+        <v>299</v>
+      </c>
+      <c r="F86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>300</v>
+      </c>
+      <c r="B87" t="s">
+        <v>113</v>
+      </c>
+      <c r="C87" t="s">
+        <v>301</v>
+      </c>
+      <c r="D87" t="s">
+        <v>302</v>
+      </c>
+      <c r="F87" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>303</v>
+      </c>
+      <c r="B88" t="s">
+        <v>304</v>
+      </c>
+      <c r="C88" t="s">
+        <v>305</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" t="s">
+        <v>306</v>
+      </c>
+      <c r="F88" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>307</v>
+      </c>
+      <c r="B89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" t="s">
+        <v>308</v>
+      </c>
+      <c r="D89" t="s">
+        <v>302</v>
+      </c>
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>309</v>
+      </c>
+      <c r="B90" t="s">
+        <v>120</v>
+      </c>
+      <c r="C90" t="s">
+        <v>310</v>
+      </c>
+      <c r="D90" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>311</v>
+      </c>
+      <c r="B91" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C91" t="s">
+        <v>312</v>
+      </c>
+      <c r="D91" t="s">
+        <v>313</v>
+      </c>
+      <c r="E91" t="s">
+        <v>314</v>
+      </c>
+      <c r="F91" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>315</v>
+      </c>
+      <c r="B92" t="s">
+        <v>279</v>
+      </c>
+      <c r="C92" t="s">
+        <v>316</v>
+      </c>
+      <c r="D92" t="s">
+        <v>317</v>
+      </c>
+      <c r="E92" t="s">
+        <v>318</v>
+      </c>
+      <c r="F92" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>319</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
+        <v>320</v>
+      </c>
+      <c r="D93" t="s">
+        <v>321</v>
+      </c>
+      <c r="E93" t="s">
+        <v>322</v>
+      </c>
+      <c r="F93" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>323</v>
+      </c>
+      <c r="B94" t="s">
+        <v>324</v>
+      </c>
+      <c r="C94" t="s">
+        <v>325</v>
+      </c>
+      <c r="D94" t="s">
+        <v>326</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>327</v>
+      </c>
+      <c r="B95" t="s">
+        <v>226</v>
+      </c>
+      <c r="C95" t="s">
+        <v>328</v>
+      </c>
+      <c r="D95" t="s">
+        <v>329</v>
+      </c>
+      <c r="F95" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>330</v>
+      </c>
+      <c r="B96" t="s">
+        <v>331</v>
+      </c>
+      <c r="C96" t="s">
+        <v>332</v>
+      </c>
+      <c r="D96" t="s">
+        <v>228</v>
+      </c>
+      <c r="F96" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>333</v>
+      </c>
+      <c r="B97" t="s">
+        <v>276</v>
+      </c>
+      <c r="C97" t="s">
+        <v>334</v>
+      </c>
+      <c r="D97" t="s">
+        <v>192</v>
+      </c>
+      <c r="E97" t="s">
+        <v>335</v>
+      </c>
+      <c r="F97" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>336</v>
+      </c>
+      <c r="B98" t="s">
+        <v>252</v>
+      </c>
+      <c r="C98" t="s">
+        <v>337</v>
+      </c>
+      <c r="D98" t="s">
+        <v>286</v>
+      </c>
+      <c r="E98" t="s">
+        <v>338</v>
+      </c>
+      <c r="F98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>339</v>
+      </c>
+      <c r="B99" t="s">
+        <v>324</v>
+      </c>
+      <c r="C99" t="s">
+        <v>340</v>
+      </c>
+      <c r="D99" t="s">
+        <v>341</v>
+      </c>
+      <c r="E99" t="s">
+        <v>342</v>
+      </c>
+      <c r="F99" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>343</v>
+      </c>
+      <c r="B100" t="s">
+        <v>226</v>
+      </c>
+      <c r="C100" t="s">
+        <v>344</v>
+      </c>
+      <c r="D100" t="s">
+        <v>345</v>
+      </c>
+      <c r="F100" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>346</v>
+      </c>
+      <c r="B101" t="s">
+        <v>195</v>
+      </c>
+      <c r="C101" t="s">
+        <v>347</v>
+      </c>
+      <c r="D101" t="s">
+        <v>228</v>
+      </c>
+      <c r="E101" t="s">
+        <v>348</v>
+      </c>
+      <c r="F101" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>349</v>
+      </c>
+      <c r="B102" t="s">
+        <v>350</v>
+      </c>
+      <c r="C102" t="s">
+        <v>351</v>
+      </c>
+      <c r="F102" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>352</v>
+      </c>
+      <c r="B103" t="s">
+        <v>353</v>
+      </c>
+      <c r="C103" t="s">
+        <v>354</v>
+      </c>
+      <c r="F103" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>355</v>
+      </c>
+      <c r="B104" t="s">
+        <v>356</v>
+      </c>
+      <c r="C104" t="s">
+        <v>357</v>
+      </c>
+      <c r="F104" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>358</v>
+      </c>
+      <c r="B105" t="s">
+        <v>359</v>
+      </c>
+      <c r="C105" t="s">
+        <v>360</v>
+      </c>
+      <c r="D105" t="s">
+        <v>286</v>
+      </c>
+      <c r="F105" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>361</v>
+      </c>
+      <c r="B106" t="s">
+        <v>252</v>
+      </c>
+      <c r="C106" t="s">
+        <v>362</v>
+      </c>
+      <c r="D106" t="s">
+        <v>26</v>
+      </c>
+      <c r="F106" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>363</v>
+      </c>
+      <c r="B107" t="s">
+        <v>364</v>
+      </c>
+      <c r="C107" t="s">
+        <v>365</v>
+      </c>
+      <c r="D107" t="s">
+        <v>341</v>
+      </c>
+      <c r="F107" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>366</v>
+      </c>
+      <c r="B108" t="s">
+        <v>50</v>
+      </c>
+      <c r="C108" t="s">
+        <v>367</v>
+      </c>
+      <c r="D108" t="s">
+        <v>368</v>
+      </c>
+      <c r="E108" t="s">
+        <v>369</v>
+      </c>
+      <c r="F108" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>370</v>
+      </c>
+      <c r="B109" t="s">
+        <v>180</v>
+      </c>
+      <c r="C109" t="s">
+        <v>371</v>
+      </c>
+      <c r="D109" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>372</v>
+      </c>
+      <c r="B110" t="s">
+        <v>373</v>
+      </c>
+      <c r="C110" t="s">
+        <v>374</v>
+      </c>
+      <c r="D110" t="s">
+        <v>375</v>
+      </c>
+      <c r="F110" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>376</v>
+      </c>
+      <c r="B111" t="s">
+        <v>60</v>
+      </c>
+      <c r="C111" t="s">
+        <v>377</v>
+      </c>
+      <c r="D111" t="s">
+        <v>99</v>
+      </c>
+      <c r="E111" t="s">
+        <v>378</v>
+      </c>
+      <c r="F111" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>379</v>
+      </c>
+      <c r="B112" t="s">
+        <v>380</v>
+      </c>
+      <c r="C112" t="s">
+        <v>381</v>
+      </c>
+      <c r="F112" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>382</v>
+      </c>
+      <c r="B113" t="s">
+        <v>383</v>
+      </c>
+      <c r="C113" t="s">
+        <v>384</v>
+      </c>
+      <c r="D113" t="s">
+        <v>26</v>
+      </c>
+      <c r="F113" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>385</v>
+      </c>
+      <c r="B114" t="s">
+        <v>386</v>
+      </c>
+      <c r="C114" t="s">
+        <v>387</v>
+      </c>
+      <c r="D114" t="s">
+        <v>286</v>
+      </c>
+      <c r="F114" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>388</v>
+      </c>
+      <c r="B115" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" t="s">
+        <v>390</v>
+      </c>
+      <c r="F115" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>391</v>
+      </c>
+      <c r="B116" t="s">
+        <v>392</v>
+      </c>
+      <c r="C116" t="s">
+        <v>393</v>
+      </c>
+      <c r="D116" t="s">
+        <v>249</v>
+      </c>
+      <c r="E116" t="s">
+        <v>394</v>
+      </c>
+      <c r="F116" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>395</v>
+      </c>
+      <c r="B117" t="s">
+        <v>396</v>
+      </c>
+      <c r="C117" t="s">
+        <v>397</v>
+      </c>
+      <c r="F117" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>398</v>
+      </c>
+      <c r="B118" t="s">
+        <v>60</v>
+      </c>
+      <c r="C118" t="s">
+        <v>399</v>
+      </c>
+      <c r="D118" t="s">
+        <v>400</v>
+      </c>
+      <c r="F118" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>401</v>
+      </c>
+      <c r="B119" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" t="s">
+        <v>402</v>
+      </c>
+      <c r="D119" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>403</v>
+      </c>
+      <c r="B120" t="s">
+        <v>404</v>
+      </c>
+      <c r="C120" t="s">
+        <v>405</v>
+      </c>
+      <c r="D120" t="s">
+        <v>26</v>
+      </c>
+      <c r="E120" t="s">
+        <v>406</v>
+      </c>
+      <c r="F120" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>407</v>
+      </c>
+      <c r="B121" t="s">
+        <v>164</v>
+      </c>
+      <c r="C121" t="s">
+        <v>408</v>
+      </c>
+      <c r="D121" t="s">
+        <v>26</v>
+      </c>
+      <c r="F121" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>409</v>
+      </c>
+      <c r="B122" t="s">
+        <v>279</v>
+      </c>
+      <c r="C122" t="s">
+        <v>410</v>
+      </c>
+      <c r="F122" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>411</v>
+      </c>
+      <c r="B123" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" t="s">
+        <v>412</v>
+      </c>
+      <c r="D123" t="s">
+        <v>413</v>
+      </c>
+      <c r="F123" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>414</v>
+      </c>
+      <c r="B124" t="s">
+        <v>210</v>
+      </c>
+      <c r="C124" t="s">
+        <v>415</v>
+      </c>
+      <c r="D124" t="s">
+        <v>416</v>
+      </c>
+      <c r="E124" t="s">
+        <v>417</v>
+      </c>
+      <c r="F124" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>418</v>
+      </c>
+      <c r="B125" t="s">
+        <v>419</v>
+      </c>
+      <c r="C125" t="s">
+        <v>420</v>
+      </c>
+      <c r="D125" t="s">
+        <v>26</v>
+      </c>
+      <c r="E125" t="s">
+        <v>421</v>
+      </c>
+      <c r="F125" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>422</v>
+      </c>
+      <c r="B126" t="s">
+        <v>60</v>
+      </c>
+      <c r="C126" t="s">
+        <v>423</v>
+      </c>
+      <c r="D126" t="s">
+        <v>26</v>
+      </c>
+      <c r="E126" t="s">
+        <v>424</v>
+      </c>
+      <c r="F126" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>425</v>
+      </c>
+      <c r="B127" t="s">
+        <v>127</v>
+      </c>
+      <c r="C127" t="s">
+        <v>426</v>
+      </c>
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>427</v>
+      </c>
+      <c r="B128" t="s">
+        <v>364</v>
+      </c>
+      <c r="C128" t="s">
+        <v>428</v>
+      </c>
+      <c r="D128" t="s">
+        <v>429</v>
+      </c>
+      <c r="F128" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>430</v>
+      </c>
+      <c r="B129" t="s">
+        <v>431</v>
+      </c>
+      <c r="C129" t="s">
+        <v>432</v>
+      </c>
+      <c r="D129" t="s">
+        <v>26</v>
+      </c>
+      <c r="F129" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>433</v>
+      </c>
+      <c r="B130" t="s">
+        <v>356</v>
+      </c>
+      <c r="C130" t="s">
+        <v>434</v>
+      </c>
+      <c r="D130" t="s">
+        <v>83</v>
+      </c>
+      <c r="F130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>435</v>
+      </c>
+      <c r="B131" t="s">
+        <v>267</v>
+      </c>
+      <c r="C131" t="s">
+        <v>436</v>
+      </c>
+      <c r="D131" t="s">
+        <v>286</v>
+      </c>
+      <c r="F131" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>437</v>
+      </c>
+      <c r="B132" t="s">
+        <v>279</v>
+      </c>
+      <c r="C132" t="s">
+        <v>438</v>
+      </c>
+      <c r="F132" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>439</v>
+      </c>
+      <c r="B133" t="s">
+        <v>440</v>
+      </c>
+      <c r="C133" t="s">
+        <v>441</v>
+      </c>
+      <c r="D133" t="s">
+        <v>99</v>
+      </c>
+      <c r="F133" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>442</v>
+      </c>
+      <c r="B134" t="s">
+        <v>356</v>
+      </c>
+      <c r="C134" t="s">
+        <v>443</v>
+      </c>
+      <c r="D134" t="s">
+        <v>444</v>
+      </c>
+      <c r="F134" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>445</v>
+      </c>
+      <c r="B135" t="s">
+        <v>446</v>
+      </c>
+      <c r="C135" t="s">
+        <v>447</v>
+      </c>
+      <c r="D135" t="s">
+        <v>345</v>
+      </c>
+      <c r="F135" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>448</v>
+      </c>
+      <c r="B136" t="s">
+        <v>449</v>
+      </c>
+      <c r="C136" t="s">
+        <v>450</v>
+      </c>
+      <c r="D136" t="s">
+        <v>26</v>
+      </c>
+      <c r="F136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>451</v>
+      </c>
+      <c r="B137" t="s">
+        <v>279</v>
+      </c>
+      <c r="C137" t="s">
+        <v>452</v>
+      </c>
+      <c r="F137" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>453</v>
+      </c>
+      <c r="B138" t="s">
+        <v>454</v>
+      </c>
+      <c r="C138" t="s">
+        <v>455</v>
+      </c>
+      <c r="D138" t="s">
+        <v>286</v>
+      </c>
+      <c r="E138" t="s">
+        <v>456</v>
+      </c>
+      <c r="F138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>457</v>
+      </c>
+      <c r="B139" t="s">
+        <v>458</v>
+      </c>
+      <c r="C139" t="s">
+        <v>459</v>
+      </c>
+      <c r="F139" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>460</v>
+      </c>
+      <c r="B140" t="s">
+        <v>461</v>
+      </c>
+      <c r="C140" t="s">
+        <v>462</v>
+      </c>
+      <c r="D140" t="s">
+        <v>463</v>
+      </c>
+      <c r="E140" t="s">
+        <v>464</v>
+      </c>
+      <c r="F140" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>465</v>
+      </c>
+      <c r="B141" t="s">
+        <v>466</v>
+      </c>
+      <c r="C141" t="s">
+        <v>467</v>
+      </c>
+      <c r="D141" t="s">
+        <v>99</v>
+      </c>
+      <c r="F141" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>468</v>
+      </c>
+      <c r="B142" t="s">
+        <v>469</v>
+      </c>
+      <c r="C142" t="s">
+        <v>470</v>
+      </c>
+      <c r="D142" t="s">
+        <v>471</v>
+      </c>
+      <c r="F142" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>472</v>
+      </c>
+      <c r="B143" t="s">
+        <v>473</v>
+      </c>
+      <c r="C143" t="s">
+        <v>474</v>
+      </c>
+      <c r="D143" t="s">
+        <v>99</v>
+      </c>
+      <c r="F143" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>475</v>
+      </c>
+      <c r="B144" t="s">
+        <v>476</v>
+      </c>
+      <c r="C144" t="s">
+        <v>477</v>
+      </c>
+      <c r="D144" t="s">
+        <v>478</v>
+      </c>
+      <c r="F144" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>479</v>
+      </c>
+      <c r="B145" t="s">
+        <v>364</v>
+      </c>
+      <c r="C145" t="s">
+        <v>480</v>
+      </c>
+      <c r="D145" t="s">
+        <v>481</v>
+      </c>
+      <c r="E145" t="s">
+        <v>482</v>
+      </c>
+      <c r="F145" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>483</v>
+      </c>
+      <c r="B146" t="s">
+        <v>484</v>
+      </c>
+      <c r="C146" t="s">
+        <v>485</v>
+      </c>
+      <c r="F146" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>486</v>
+      </c>
+      <c r="B147" t="s">
+        <v>487</v>
+      </c>
+      <c r="C147" t="s">
+        <v>488</v>
+      </c>
+      <c r="F147" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>489</v>
+      </c>
+      <c r="B148" t="s">
+        <v>490</v>
+      </c>
+      <c r="C148" t="s">
+        <v>491</v>
+      </c>
+      <c r="D148" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" t="s">
+        <v>492</v>
+      </c>
+      <c r="F148" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>493</v>
+      </c>
+      <c r="B149" t="s">
+        <v>494</v>
+      </c>
+      <c r="C149" t="s">
+        <v>495</v>
+      </c>
+      <c r="D149" t="s">
+        <v>496</v>
+      </c>
+      <c r="E149" t="s">
+        <v>497</v>
+      </c>
+      <c r="F149" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>498</v>
+      </c>
+      <c r="B150" t="s">
+        <v>499</v>
+      </c>
+      <c r="C150" t="s">
+        <v>500</v>
+      </c>
+      <c r="D150" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" t="s">
+        <v>501</v>
+      </c>
+      <c r="F150" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>502</v>
+      </c>
+      <c r="B151" t="s">
+        <v>503</v>
+      </c>
+      <c r="C151" t="s">
+        <v>504</v>
+      </c>
+      <c r="D151" t="s">
+        <v>106</v>
+      </c>
+      <c r="E151" t="s">
+        <v>505</v>
+      </c>
+      <c r="F151" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>506</v>
+      </c>
+      <c r="B152" t="s">
+        <v>507</v>
+      </c>
+      <c r="C152" t="s">
+        <v>508</v>
+      </c>
+      <c r="D152" t="s">
+        <v>26</v>
+      </c>
+      <c r="F152" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>509</v>
+      </c>
+      <c r="B153" t="s">
+        <v>510</v>
+      </c>
+      <c r="C153" t="s">
+        <v>511</v>
+      </c>
+      <c r="D153" t="s">
+        <v>106</v>
+      </c>
+      <c r="E153" t="s">
+        <v>512</v>
+      </c>
+      <c r="F153" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>513</v>
+      </c>
+      <c r="B154" t="s">
+        <v>514</v>
+      </c>
+      <c r="C154" t="s">
+        <v>515</v>
+      </c>
+      <c r="D154" t="s">
+        <v>40</v>
+      </c>
+      <c r="F154" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>516</v>
+      </c>
+      <c r="B155" t="s">
+        <v>517</v>
+      </c>
+      <c r="C155" t="s">
+        <v>518</v>
+      </c>
+      <c r="F155" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>519</v>
+      </c>
+      <c r="B156" t="s">
+        <v>520</v>
+      </c>
+      <c r="C156" t="s">
+        <v>521</v>
+      </c>
+      <c r="D156" t="s">
+        <v>83</v>
+      </c>
+      <c r="F156" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>522</v>
+      </c>
+      <c r="B157" t="s">
+        <v>499</v>
+      </c>
+      <c r="C157" t="s">
+        <v>523</v>
+      </c>
+      <c r="D157" t="s">
+        <v>99</v>
+      </c>
+      <c r="F157" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>524</v>
+      </c>
+      <c r="B158" t="s">
+        <v>525</v>
+      </c>
+      <c r="C158" t="s">
+        <v>526</v>
+      </c>
+      <c r="D158" t="s">
+        <v>99</v>
+      </c>
+      <c r="F158" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>527</v>
+      </c>
+      <c r="B159" t="s">
+        <v>528</v>
+      </c>
+      <c r="C159" t="s">
+        <v>529</v>
+      </c>
+      <c r="D159" t="s">
+        <v>40</v>
+      </c>
+      <c r="F159" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>530</v>
+      </c>
+      <c r="B160" t="s">
+        <v>531</v>
+      </c>
+      <c r="C160" t="s">
+        <v>532</v>
+      </c>
+      <c r="D160" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" t="s">
+        <v>533</v>
+      </c>
+      <c r="F160" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>534</v>
+      </c>
+      <c r="B161" t="s">
+        <v>535</v>
+      </c>
+      <c r="C161" t="s">
+        <v>536</v>
+      </c>
+      <c r="D161" t="s">
+        <v>313</v>
+      </c>
+      <c r="F161" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>537</v>
+      </c>
+      <c r="B162" t="s">
+        <v>538</v>
+      </c>
+      <c r="C162" t="s">
+        <v>539</v>
+      </c>
+      <c r="D162" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>540</v>
+      </c>
+      <c r="B163" t="s">
+        <v>541</v>
+      </c>
+      <c r="C163" t="s">
+        <v>542</v>
+      </c>
+      <c r="D163" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>543</v>
+      </c>
+      <c r="B164" t="s">
+        <v>544</v>
+      </c>
+      <c r="C164" t="s">
+        <v>545</v>
+      </c>
+      <c r="D164" t="s">
+        <v>274</v>
+      </c>
+      <c r="E164" t="s">
+        <v>546</v>
+      </c>
+      <c r="F164" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>547</v>
+      </c>
+      <c r="B165" t="s">
+        <v>548</v>
+      </c>
+      <c r="C165" t="s">
+        <v>549</v>
+      </c>
+      <c r="D165" t="s">
+        <v>106</v>
+      </c>
+      <c r="E165" t="s">
+        <v>550</v>
+      </c>
+      <c r="F165" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>551</v>
+      </c>
+      <c r="B166" t="s">
+        <v>552</v>
+      </c>
+      <c r="C166" t="s">
+        <v>553</v>
+      </c>
+      <c r="F166" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>554</v>
+      </c>
+      <c r="B167" t="s">
+        <v>555</v>
+      </c>
+      <c r="C167" t="s">
+        <v>556</v>
+      </c>
+      <c r="D167" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="E167" t="s">
+        <v>557</v>
+      </c>
+      <c r="F167" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>558</v>
+      </c>
+      <c r="B168" t="s">
+        <v>559</v>
+      </c>
+      <c r="C168" t="s">
+        <v>560</v>
+      </c>
+      <c r="F168" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>561</v>
+      </c>
+      <c r="B169" t="s">
+        <v>499</v>
+      </c>
+      <c r="C169" t="s">
+        <v>562</v>
+      </c>
+      <c r="D169" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" t="s">
+        <v>563</v>
+      </c>
+      <c r="F169" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>564</v>
+      </c>
+      <c r="B170" t="s">
+        <v>535</v>
+      </c>
+      <c r="C170" t="s">
+        <v>565</v>
+      </c>
+      <c r="D170" t="s">
+        <v>566</v>
+      </c>
+      <c r="F170" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>567</v>
+      </c>
+      <c r="B171" t="s">
+        <v>568</v>
+      </c>
+      <c r="C171" t="s">
+        <v>569</v>
+      </c>
+      <c r="D171" t="s">
+        <v>91</v>
+      </c>
+      <c r="F171" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>570</v>
+      </c>
+      <c r="B172" t="s">
+        <v>520</v>
+      </c>
+      <c r="C172" t="s">
+        <v>571</v>
+      </c>
+      <c r="D172" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="E172" t="s">
+        <v>572</v>
+      </c>
+      <c r="F172" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>573</v>
+      </c>
+      <c r="B173" t="s">
+        <v>574</v>
+      </c>
+      <c r="C173" t="s">
+        <v>575</v>
+      </c>
+      <c r="D173" t="s">
+        <v>9</v>
+      </c>
+      <c r="F173" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>576</v>
+      </c>
+      <c r="B174" t="s">
+        <v>577</v>
+      </c>
+      <c r="C174" t="s">
+        <v>578</v>
+      </c>
+      <c r="D174" t="s">
+        <v>579</v>
+      </c>
+      <c r="E174" t="s">
+        <v>580</v>
+      </c>
+      <c r="F174" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>581</v>
+      </c>
+      <c r="B175" t="s">
+        <v>582</v>
+      </c>
+      <c r="C175" t="s">
+        <v>583</v>
+      </c>
+      <c r="D175" t="s">
+        <v>584</v>
+      </c>
+      <c r="F175" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>585</v>
+      </c>
+      <c r="B176" t="s">
+        <v>586</v>
+      </c>
+      <c r="C176" t="s">
+        <v>587</v>
+      </c>
+      <c r="F176" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>588</v>
+      </c>
+      <c r="B177" t="s">
         <v>33</v>
       </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="C177" t="s">
+        <v>589</v>
+      </c>
+      <c r="D177" t="s">
+        <v>9</v>
+      </c>
+      <c r="F177" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>590</v>
+      </c>
+      <c r="B178" t="s">
+        <v>591</v>
+      </c>
+      <c r="C178" t="s">
+        <v>592</v>
+      </c>
+      <c r="D178" t="s">
+        <v>345</v>
+      </c>
+      <c r="E178" t="s">
+        <v>593</v>
+      </c>
+      <c r="F178" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>594</v>
+      </c>
+      <c r="B179" t="s">
+        <v>595</v>
+      </c>
+      <c r="C179" t="s">
+        <v>596</v>
+      </c>
+      <c r="D179" t="s">
+        <v>597</v>
+      </c>
+      <c r="E179" t="s">
+        <v>598</v>
+      </c>
+      <c r="F179" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>599</v>
+      </c>
+      <c r="B180" t="s">
+        <v>568</v>
+      </c>
+      <c r="C180" t="s">
+        <v>600</v>
+      </c>
+      <c r="D180" t="s">
+        <v>601</v>
+      </c>
+      <c r="F180" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>602</v>
+      </c>
+      <c r="B181" t="s">
+        <v>603</v>
+      </c>
+      <c r="C181" t="s">
+        <v>604</v>
+      </c>
+      <c r="D181" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="F181" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>605</v>
+      </c>
+      <c r="B182" t="s">
+        <v>606</v>
+      </c>
+      <c r="C182" t="s">
+        <v>607</v>
+      </c>
+      <c r="F182" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>608</v>
+      </c>
+      <c r="B183" t="s">
+        <v>609</v>
+      </c>
+      <c r="C183" t="s">
+        <v>610</v>
+      </c>
+      <c r="D183" t="s">
+        <v>566</v>
+      </c>
+      <c r="E183" t="s">
+        <v>611</v>
+      </c>
+      <c r="F183" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>612</v>
+      </c>
+      <c r="B184" t="s">
+        <v>613</v>
+      </c>
+      <c r="C184" t="s">
+        <v>614</v>
+      </c>
+      <c r="F184" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>615</v>
+      </c>
+      <c r="B185" t="s">
+        <v>616</v>
+      </c>
+      <c r="C185" t="s">
+        <v>617</v>
+      </c>
+      <c r="D185" t="s">
+        <v>9</v>
+      </c>
+      <c r="F185" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>618</v>
+      </c>
+      <c r="B186" t="s">
+        <v>619</v>
+      </c>
+      <c r="C186" t="s">
+        <v>620</v>
+      </c>
+      <c r="D186" t="s">
+        <v>40</v>
+      </c>
+      <c r="F186" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>621</v>
+      </c>
+      <c r="B187" t="s">
+        <v>622</v>
+      </c>
+      <c r="C187" t="s">
+        <v>623</v>
+      </c>
+      <c r="D187" t="s">
+        <v>624</v>
+      </c>
+      <c r="F187" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>625</v>
+      </c>
+      <c r="B188" t="s">
+        <v>626</v>
+      </c>
+      <c r="C188" t="s">
+        <v>627</v>
+      </c>
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
+      <c r="F188" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>628</v>
+      </c>
+      <c r="B189" t="s">
+        <v>574</v>
+      </c>
+      <c r="C189" t="s">
+        <v>629</v>
+      </c>
+      <c r="D189" t="s">
+        <v>630</v>
+      </c>
+      <c r="E189" t="s">
+        <v>631</v>
+      </c>
+      <c r="F189" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>632</v>
+      </c>
+      <c r="B190" t="s">
+        <v>633</v>
+      </c>
+      <c r="C190" t="s">
+        <v>634</v>
+      </c>
+      <c r="F190" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>635</v>
+      </c>
+      <c r="B191" t="s">
+        <v>636</v>
+      </c>
+      <c r="C191" t="s">
+        <v>637</v>
+      </c>
+      <c r="D191" t="s">
         <v>91</v>
       </c>
-      <c r="B34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>97</v>
-      </c>
-      <c r="B36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>101</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>103</v>
-      </c>
-      <c r="B39" t="s">
-        <v>104</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
+      <c r="E191" t="s">
+        <v>638</v>
+      </c>
+      <c r="F191" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>639</v>
+      </c>
+      <c r="B192" t="s">
+        <v>640</v>
+      </c>
+      <c r="C192" t="s">
+        <v>641</v>
+      </c>
+      <c r="D192" t="s">
+        <v>642</v>
+      </c>
+      <c r="E192" t="s">
+        <v>643</v>
+      </c>
+      <c r="F192" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>644</v>
+      </c>
+      <c r="B193" t="s">
+        <v>645</v>
+      </c>
+      <c r="C193" t="s">
+        <v>646</v>
+      </c>
+      <c r="D193" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>647</v>
+      </c>
+      <c r="B194" t="s">
+        <v>648</v>
+      </c>
+      <c r="C194" t="s">
+        <v>649</v>
+      </c>
+      <c r="D194" t="s">
         <v>106</v>
       </c>
-      <c r="B40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>111</v>
-      </c>
-      <c r="B42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B43" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>116</v>
-      </c>
-      <c r="B44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>118</v>
-      </c>
-      <c r="B45" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>121</v>
-      </c>
-      <c r="B46" t="s">
-        <v>39</v>
-      </c>
-      <c r="C46" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>123</v>
-      </c>
-      <c r="B47" t="s">
-        <v>124</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="E194" t="s">
+        <v>650</v>
+      </c>
+      <c r="F194" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>651</v>
+      </c>
+      <c r="B195" t="s">
+        <v>652</v>
+      </c>
+      <c r="C195" t="s">
+        <v>653</v>
+      </c>
+      <c r="D195" t="s">
+        <v>40</v>
+      </c>
+      <c r="F195" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>654</v>
+      </c>
+      <c r="B196" t="s">
+        <v>655</v>
+      </c>
+      <c r="C196" t="s">
+        <v>656</v>
+      </c>
+      <c r="D196" t="s">
+        <v>40</v>
+      </c>
+      <c r="E196" t="s">
+        <v>657</v>
+      </c>
+      <c r="F196" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>658</v>
+      </c>
+      <c r="B197" t="s">
+        <v>659</v>
+      </c>
+      <c r="C197" t="s">
+        <v>660</v>
+      </c>
+      <c r="D197" t="s">
+        <v>661</v>
+      </c>
+      <c r="E197" t="s">
+        <v>662</v>
+      </c>
+      <c r="F197" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>663</v>
+      </c>
+      <c r="B198" t="s">
+        <v>664</v>
+      </c>
+      <c r="C198" t="s">
+        <v>665</v>
+      </c>
+      <c r="D198" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>666</v>
+      </c>
+      <c r="B199" t="s">
+        <v>667</v>
+      </c>
+      <c r="C199" t="s">
+        <v>668</v>
+      </c>
+      <c r="D199" t="s">
+        <v>669</v>
+      </c>
+      <c r="F199" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>670</v>
+      </c>
+      <c r="B200" t="s">
+        <v>671</v>
+      </c>
+      <c r="C200" t="s">
+        <v>672</v>
+      </c>
+      <c r="D200" t="s">
+        <v>106</v>
+      </c>
+      <c r="E200" t="s">
+        <v>673</v>
+      </c>
+      <c r="F200" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>674</v>
+      </c>
+      <c r="B201" t="s">
+        <v>675</v>
+      </c>
+      <c r="C201" t="s">
+        <v>676</v>
+      </c>
+      <c r="D201" t="s">
+        <v>152</v>
+      </c>
+      <c r="F201" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>677</v>
+      </c>
+      <c r="B202" t="s">
+        <v>678</v>
+      </c>
+      <c r="C202" t="s">
+        <v>679</v>
+      </c>
+      <c r="D202" t="s">
+        <v>680</v>
+      </c>
+      <c r="E202" t="s">
+        <v>681</v>
+      </c>
+      <c r="F202" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>682</v>
+      </c>
+      <c r="B203" t="s">
+        <v>683</v>
+      </c>
+      <c r="C203" t="s">
+        <v>684</v>
+      </c>
+      <c r="D203" t="s">
+        <v>274</v>
+      </c>
+      <c r="F203" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>685</v>
+      </c>
+      <c r="B204" t="s">
+        <v>686</v>
+      </c>
+      <c r="C204" t="s">
+        <v>687</v>
+      </c>
+      <c r="D204" t="s">
+        <v>129</v>
+      </c>
+      <c r="E204" t="s">
+        <v>688</v>
+      </c>
+      <c r="F204" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>689</v>
+      </c>
+      <c r="B205" t="s">
+        <v>690</v>
+      </c>
+      <c r="C205" t="s">
+        <v>691</v>
+      </c>
+      <c r="D205" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>126</v>
-      </c>
-      <c r="B48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>128</v>
-      </c>
-      <c r="B49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="F205" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
+        <v>692</v>
+      </c>
+      <c r="B206" t="s">
+        <v>693</v>
+      </c>
+      <c r="C206" t="s">
+        <v>694</v>
+      </c>
+      <c r="D206" t="s">
+        <v>91</v>
+      </c>
+      <c r="F206" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>695</v>
+      </c>
+      <c r="B207" t="s">
+        <v>696</v>
+      </c>
+      <c r="C207" t="s">
+        <v>697</v>
+      </c>
+      <c r="D207" t="s">
+        <v>106</v>
+      </c>
+      <c r="F207" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>698</v>
+      </c>
+      <c r="B208" t="s">
+        <v>699</v>
+      </c>
+      <c r="C208" t="s">
+        <v>700</v>
+      </c>
+      <c r="D208" t="s">
+        <v>345</v>
+      </c>
+      <c r="F208" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>701</v>
+      </c>
+      <c r="B209" t="s">
+        <v>702</v>
+      </c>
+      <c r="C209" t="s">
+        <v>703</v>
+      </c>
+      <c r="D209" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>130</v>
-      </c>
-      <c r="B50" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>133</v>
-      </c>
-      <c r="B51" t="s">
-        <v>134</v>
-      </c>
-      <c r="C51" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>136</v>
-      </c>
-      <c r="B52" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>138</v>
-      </c>
-      <c r="B53" t="s">
-        <v>139</v>
-      </c>
-      <c r="C53" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>141</v>
-      </c>
-      <c r="B54" t="s">
-        <v>142</v>
-      </c>
-      <c r="C54" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
-        <v>144</v>
-      </c>
-      <c r="B55" t="s">
-        <v>145</v>
-      </c>
-      <c r="C55" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>147</v>
-      </c>
-      <c r="B56" t="s">
-        <v>148</v>
-      </c>
-      <c r="C56" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>150</v>
-      </c>
-      <c r="B57" t="s">
-        <v>151</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="E209" t="s">
+        <v>704</v>
+      </c>
+      <c r="F209" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>705</v>
+      </c>
+      <c r="B210" t="s">
+        <v>706</v>
+      </c>
+      <c r="C210" t="s">
+        <v>707</v>
+      </c>
+      <c r="F210" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>708</v>
+      </c>
+      <c r="B211" t="s">
+        <v>709</v>
+      </c>
+      <c r="C211" t="s">
+        <v>710</v>
+      </c>
+      <c r="D211" t="s">
+        <v>9</v>
+      </c>
+      <c r="F211" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>711</v>
+      </c>
+      <c r="B212" t="s">
+        <v>712</v>
+      </c>
+      <c r="C212" t="s">
+        <v>713</v>
+      </c>
+      <c r="D212" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>153</v>
-      </c>
-      <c r="B58" t="s">
-        <v>154</v>
-      </c>
-      <c r="C58" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>156</v>
-      </c>
-      <c r="B59" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>158</v>
-      </c>
-      <c r="B60" t="s">
-        <v>145</v>
-      </c>
-      <c r="C60" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>160</v>
-      </c>
-      <c r="B61" t="s">
-        <v>161</v>
-      </c>
-      <c r="C61" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>163</v>
-      </c>
-      <c r="B62" t="s">
-        <v>82</v>
-      </c>
-      <c r="C62" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>165</v>
-      </c>
-      <c r="B63" t="s">
-        <v>166</v>
-      </c>
-      <c r="C63" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>168</v>
-      </c>
-      <c r="B64" t="s">
-        <v>169</v>
-      </c>
-      <c r="C64" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>171</v>
-      </c>
-      <c r="B65" t="s">
-        <v>172</v>
-      </c>
-      <c r="C65" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>174</v>
-      </c>
-      <c r="B66" t="s">
-        <v>175</v>
-      </c>
-      <c r="C66" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>177</v>
-      </c>
-      <c r="B67" t="s">
-        <v>19</v>
-      </c>
-      <c r="C67" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>179</v>
-      </c>
-      <c r="B68" t="s">
-        <v>166</v>
-      </c>
-      <c r="C68" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>181</v>
-      </c>
-      <c r="B69" t="s">
-        <v>182</v>
-      </c>
-      <c r="C69" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>184</v>
-      </c>
-      <c r="B70" t="s">
-        <v>39</v>
-      </c>
-      <c r="C70" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
-        <v>186</v>
-      </c>
-      <c r="B71" t="s">
-        <v>187</v>
-      </c>
-      <c r="C71" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
-        <v>189</v>
-      </c>
-      <c r="B72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C72" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>191</v>
-      </c>
-      <c r="B73" t="s">
-        <v>192</v>
-      </c>
-      <c r="C73" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>194</v>
-      </c>
-      <c r="B74" t="s">
-        <v>195</v>
-      </c>
-      <c r="C74" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
-        <v>197</v>
-      </c>
-      <c r="B75" t="s">
-        <v>56</v>
-      </c>
-      <c r="C75" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
-        <v>199</v>
-      </c>
-      <c r="B76" t="s">
-        <v>200</v>
-      </c>
-      <c r="C76" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>202</v>
-      </c>
-      <c r="B77" t="s">
-        <v>87</v>
-      </c>
-      <c r="C77" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
-        <v>204</v>
-      </c>
-      <c r="B78" t="s">
-        <v>205</v>
-      </c>
-      <c r="C78" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
-        <v>207</v>
-      </c>
-      <c r="B79" t="s">
-        <v>208</v>
-      </c>
-      <c r="C79" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" t="s">
-        <v>210</v>
-      </c>
-      <c r="B80" t="s">
-        <v>211</v>
-      </c>
-      <c r="C80" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>213</v>
-      </c>
-      <c r="B81" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" t="s">
-        <v>215</v>
-      </c>
-      <c r="B82" t="s">
-        <v>36</v>
-      </c>
-      <c r="C82" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" t="s">
-        <v>217</v>
-      </c>
-      <c r="B83" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" t="s">
-        <v>219</v>
-      </c>
-      <c r="B84" t="s">
-        <v>208</v>
-      </c>
-      <c r="C84" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" t="s">
-        <v>221</v>
-      </c>
-      <c r="B85" t="s">
-        <v>222</v>
-      </c>
-      <c r="C85" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" t="s">
-        <v>224</v>
-      </c>
-      <c r="B86" t="s">
-        <v>225</v>
-      </c>
-      <c r="C86" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" t="s">
-        <v>227</v>
-      </c>
-      <c r="B87" t="s">
-        <v>82</v>
-      </c>
-      <c r="C87" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" t="s">
-        <v>229</v>
-      </c>
-      <c r="B88" t="s">
-        <v>230</v>
-      </c>
-      <c r="C88" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" t="s">
-        <v>232</v>
-      </c>
-      <c r="B89" t="s">
-        <v>19</v>
-      </c>
-      <c r="C89" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" t="s">
-        <v>234</v>
-      </c>
-      <c r="B90" t="s">
-        <v>87</v>
-      </c>
-      <c r="C90" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" t="s">
-        <v>236</v>
-      </c>
-      <c r="B91" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" t="s">
-        <v>238</v>
-      </c>
-      <c r="B92" t="s">
-        <v>211</v>
-      </c>
-      <c r="C92" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" t="s">
-        <v>240</v>
-      </c>
-      <c r="B93" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" t="s">
-        <v>242</v>
-      </c>
-      <c r="B94" t="s">
-        <v>243</v>
-      </c>
-      <c r="C94" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" t="s">
-        <v>245</v>
-      </c>
-      <c r="B95" t="s">
-        <v>166</v>
-      </c>
-      <c r="C95" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" t="s">
-        <v>247</v>
-      </c>
-      <c r="B96" t="s">
-        <v>248</v>
-      </c>
-      <c r="C96" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" t="s">
-        <v>250</v>
-      </c>
-      <c r="B97" t="s">
-        <v>208</v>
-      </c>
-      <c r="C97" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" t="s">
-        <v>252</v>
-      </c>
-      <c r="B98" t="s">
-        <v>187</v>
-      </c>
-      <c r="C98" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" t="s">
-        <v>254</v>
-      </c>
-      <c r="B99" t="s">
-        <v>243</v>
-      </c>
-      <c r="C99" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" t="s">
-        <v>256</v>
-      </c>
-      <c r="B100" t="s">
-        <v>166</v>
-      </c>
-      <c r="C100" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" t="s">
-        <v>258</v>
-      </c>
-      <c r="B101" t="s">
-        <v>142</v>
-      </c>
-      <c r="C101" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" t="s">
-        <v>260</v>
-      </c>
-      <c r="B102" t="s">
-        <v>261</v>
-      </c>
-      <c r="C102" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" t="s">
-        <v>263</v>
-      </c>
-      <c r="B103" t="s">
-        <v>264</v>
-      </c>
-      <c r="C103" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" t="s">
-        <v>266</v>
-      </c>
-      <c r="B104" t="s">
-        <v>267</v>
-      </c>
-      <c r="C104" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" t="s">
-        <v>269</v>
-      </c>
-      <c r="B105" t="s">
-        <v>270</v>
-      </c>
-      <c r="C105" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" t="s">
-        <v>272</v>
-      </c>
-      <c r="B106" t="s">
-        <v>187</v>
-      </c>
-      <c r="C106" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" t="s">
-        <v>274</v>
-      </c>
-      <c r="B107" t="s">
-        <v>275</v>
-      </c>
-      <c r="C107" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" t="s">
-        <v>277</v>
-      </c>
-      <c r="B108" t="s">
-        <v>36</v>
-      </c>
-      <c r="C108" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" t="s">
-        <v>279</v>
-      </c>
-      <c r="B109" t="s">
-        <v>131</v>
-      </c>
-      <c r="C109" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" t="s">
-        <v>281</v>
-      </c>
-      <c r="B110" t="s">
-        <v>282</v>
-      </c>
-      <c r="C110" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" t="s">
-        <v>284</v>
-      </c>
-      <c r="B111" t="s">
-        <v>44</v>
-      </c>
-      <c r="C111" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" t="s">
-        <v>286</v>
-      </c>
-      <c r="B112" t="s">
-        <v>287</v>
-      </c>
-      <c r="C112" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" t="s">
-        <v>289</v>
-      </c>
-      <c r="B113" t="s">
-        <v>290</v>
-      </c>
-      <c r="C113" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" t="s">
-        <v>292</v>
-      </c>
-      <c r="B114" t="s">
-        <v>293</v>
-      </c>
-      <c r="C114" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" t="s">
-        <v>295</v>
-      </c>
-      <c r="B115" t="s">
-        <v>296</v>
-      </c>
-      <c r="C115" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" t="s">
-        <v>298</v>
-      </c>
-      <c r="B116" t="s">
-        <v>299</v>
-      </c>
-      <c r="C116" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" t="s">
-        <v>301</v>
-      </c>
-      <c r="B117" t="s">
-        <v>302</v>
-      </c>
-      <c r="C117" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" t="s">
-        <v>304</v>
-      </c>
-      <c r="B118" t="s">
-        <v>44</v>
-      </c>
-      <c r="C118" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" t="s">
-        <v>306</v>
-      </c>
-      <c r="B119" t="s">
-        <v>4</v>
-      </c>
-      <c r="C119" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" t="s">
-        <v>308</v>
-      </c>
-      <c r="B120" t="s">
-        <v>309</v>
-      </c>
-      <c r="C120" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" t="s">
-        <v>311</v>
-      </c>
-      <c r="B121" t="s">
-        <v>119</v>
-      </c>
-      <c r="C121" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" t="s">
-        <v>313</v>
-      </c>
-      <c r="B122" t="s">
-        <v>211</v>
-      </c>
-      <c r="C122" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" t="s">
-        <v>315</v>
-      </c>
-      <c r="B123" t="s">
-        <v>275</v>
-      </c>
-      <c r="C123" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" t="s">
-        <v>317</v>
-      </c>
-      <c r="B124" t="s">
-        <v>154</v>
-      </c>
-      <c r="C124" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" t="s">
-        <v>319</v>
-      </c>
-      <c r="B125" t="s">
-        <v>320</v>
-      </c>
-      <c r="C125" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" t="s">
-        <v>322</v>
-      </c>
-      <c r="B126" t="s">
-        <v>44</v>
-      </c>
-      <c r="C126" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" t="s">
-        <v>324</v>
-      </c>
-      <c r="B127" t="s">
-        <v>92</v>
-      </c>
-      <c r="C127" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" t="s">
-        <v>326</v>
-      </c>
-      <c r="B128" t="s">
-        <v>275</v>
-      </c>
-      <c r="C128" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" t="s">
-        <v>328</v>
-      </c>
-      <c r="B129" t="s">
-        <v>329</v>
-      </c>
-      <c r="C129" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" t="s">
-        <v>331</v>
-      </c>
-      <c r="B130" t="s">
-        <v>267</v>
-      </c>
-      <c r="C130" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" t="s">
-        <v>333</v>
-      </c>
-      <c r="B131" t="s">
-        <v>200</v>
-      </c>
-      <c r="C131" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" t="s">
-        <v>335</v>
-      </c>
-      <c r="B132" t="s">
-        <v>211</v>
-      </c>
-      <c r="C132" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" t="s">
-        <v>337</v>
-      </c>
-      <c r="B133" t="s">
-        <v>338</v>
-      </c>
-      <c r="C133" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" t="s">
-        <v>340</v>
-      </c>
-      <c r="B134" t="s">
-        <v>267</v>
-      </c>
-      <c r="C134" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" t="s">
-        <v>342</v>
-      </c>
-      <c r="B135" t="s">
-        <v>343</v>
-      </c>
-      <c r="C135" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" t="s">
-        <v>345</v>
-      </c>
-      <c r="B136" t="s">
-        <v>346</v>
-      </c>
-      <c r="C136" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" t="s">
-        <v>348</v>
-      </c>
-      <c r="B137" t="s">
-        <v>211</v>
-      </c>
-      <c r="C137" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" t="s">
-        <v>350</v>
-      </c>
-      <c r="B138" t="s">
-        <v>351</v>
-      </c>
-      <c r="C138" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" t="s">
-        <v>353</v>
-      </c>
-      <c r="B139" t="s">
-        <v>354</v>
-      </c>
-      <c r="C139" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" t="s">
-        <v>356</v>
-      </c>
-      <c r="B140" t="s">
-        <v>357</v>
-      </c>
-      <c r="C140" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" t="s">
-        <v>359</v>
-      </c>
-      <c r="B141" t="s">
-        <v>360</v>
-      </c>
-      <c r="C141" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" t="s">
-        <v>362</v>
-      </c>
-      <c r="B142" t="s">
-        <v>363</v>
-      </c>
-      <c r="C142" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143" t="s">
-        <v>365</v>
-      </c>
-      <c r="B143" t="s">
-        <v>366</v>
-      </c>
-      <c r="C143" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" t="s">
-        <v>368</v>
-      </c>
-      <c r="B144" t="s">
-        <v>369</v>
-      </c>
-      <c r="C144" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" t="s">
-        <v>371</v>
-      </c>
-      <c r="B145" t="s">
-        <v>275</v>
-      </c>
-      <c r="C145" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" t="s">
-        <v>373</v>
-      </c>
-      <c r="B146" t="s">
-        <v>374</v>
-      </c>
-      <c r="C146" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" t="s">
-        <v>376</v>
-      </c>
-      <c r="B147" t="s">
-        <v>377</v>
-      </c>
-      <c r="C147" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" t="s">
-        <v>379</v>
-      </c>
-      <c r="B148" t="s">
-        <v>380</v>
-      </c>
-      <c r="C148" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" t="s">
-        <v>382</v>
-      </c>
-      <c r="B149" t="s">
-        <v>383</v>
-      </c>
-      <c r="C149" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" t="s">
-        <v>385</v>
-      </c>
-      <c r="B150" t="s">
-        <v>386</v>
-      </c>
-      <c r="C150" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" t="s">
-        <v>388</v>
-      </c>
-      <c r="B151" t="s">
-        <v>389</v>
-      </c>
-      <c r="C151" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" t="s">
-        <v>391</v>
-      </c>
-      <c r="B152" t="s">
-        <v>392</v>
-      </c>
-      <c r="C152" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" t="s">
-        <v>394</v>
-      </c>
-      <c r="B153" t="s">
-        <v>395</v>
-      </c>
-      <c r="C153" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" t="s">
-        <v>397</v>
-      </c>
-      <c r="B154" t="s">
-        <v>398</v>
-      </c>
-      <c r="C154" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" t="s">
-        <v>400</v>
-      </c>
-      <c r="B155" t="s">
-        <v>401</v>
-      </c>
-      <c r="C155" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" t="s">
-        <v>403</v>
-      </c>
-      <c r="B156" t="s">
-        <v>404</v>
-      </c>
-      <c r="C156" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" t="s">
-        <v>406</v>
-      </c>
-      <c r="B157" t="s">
-        <v>386</v>
-      </c>
-      <c r="C157" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" t="s">
-        <v>408</v>
-      </c>
-      <c r="B158" t="s">
-        <v>409</v>
-      </c>
-      <c r="C158" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" t="s">
-        <v>411</v>
-      </c>
-      <c r="B159" t="s">
-        <v>412</v>
-      </c>
-      <c r="C159" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" t="s">
-        <v>414</v>
-      </c>
-      <c r="B160" t="s">
-        <v>415</v>
-      </c>
-      <c r="C160" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161" t="s">
-        <v>417</v>
-      </c>
-      <c r="B161" t="s">
-        <v>418</v>
-      </c>
-      <c r="C161" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" t="s">
-        <v>420</v>
-      </c>
-      <c r="B162" t="s">
-        <v>421</v>
-      </c>
-      <c r="C162" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163" t="s">
-        <v>423</v>
-      </c>
-      <c r="B163" t="s">
-        <v>424</v>
-      </c>
-      <c r="C163" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" t="s">
-        <v>426</v>
-      </c>
-      <c r="B164" t="s">
-        <v>427</v>
-      </c>
-      <c r="C164" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" t="s">
-        <v>429</v>
-      </c>
-      <c r="B165" t="s">
-        <v>430</v>
-      </c>
-      <c r="C165" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" t="s">
-        <v>432</v>
-      </c>
-      <c r="B166" t="s">
-        <v>433</v>
-      </c>
-      <c r="C166" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" t="s">
-        <v>435</v>
-      </c>
-      <c r="B167" t="s">
-        <v>436</v>
-      </c>
-      <c r="C167" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" t="s">
-        <v>438</v>
-      </c>
-      <c r="B168" t="s">
-        <v>439</v>
-      </c>
-      <c r="C168" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" t="s">
-        <v>441</v>
-      </c>
-      <c r="B169" t="s">
-        <v>386</v>
-      </c>
-      <c r="C169" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" t="s">
-        <v>443</v>
-      </c>
-      <c r="B170" t="s">
-        <v>418</v>
-      </c>
-      <c r="C170" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" t="s">
-        <v>445</v>
-      </c>
-      <c r="B171" t="s">
-        <v>446</v>
-      </c>
-      <c r="C171" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" t="s">
-        <v>448</v>
-      </c>
-      <c r="B172" t="s">
-        <v>404</v>
-      </c>
-      <c r="C172" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3">
-      <c r="A173" t="s">
-        <v>450</v>
-      </c>
-      <c r="B173" t="s">
-        <v>451</v>
-      </c>
-      <c r="C173" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3">
-      <c r="A174" t="s">
-        <v>453</v>
-      </c>
-      <c r="B174" t="s">
-        <v>454</v>
-      </c>
-      <c r="C174" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" t="s">
-        <v>456</v>
-      </c>
-      <c r="B175" t="s">
-        <v>457</v>
-      </c>
-      <c r="C175" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176" t="s">
-        <v>459</v>
-      </c>
-      <c r="B176" t="s">
-        <v>460</v>
-      </c>
-      <c r="C176" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" t="s">
-        <v>462</v>
-      </c>
-      <c r="B177" t="s">
-        <v>22</v>
-      </c>
-      <c r="C177" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178" t="s">
-        <v>464</v>
-      </c>
-      <c r="B178" t="s">
-        <v>465</v>
-      </c>
-      <c r="C178" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179" t="s">
-        <v>467</v>
-      </c>
-      <c r="B179" t="s">
-        <v>468</v>
-      </c>
-      <c r="C179" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="A180" t="s">
-        <v>470</v>
-      </c>
-      <c r="B180" t="s">
-        <v>446</v>
-      </c>
-      <c r="C180" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3">
-      <c r="A181" t="s">
-        <v>472</v>
-      </c>
-      <c r="B181" t="s">
-        <v>473</v>
-      </c>
-      <c r="C181" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" t="s">
-        <v>475</v>
-      </c>
-      <c r="B182" t="s">
-        <v>476</v>
-      </c>
-      <c r="C182" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183" t="s">
-        <v>478</v>
-      </c>
-      <c r="B183" t="s">
-        <v>479</v>
-      </c>
-      <c r="C183" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" t="s">
-        <v>481</v>
-      </c>
-      <c r="B184" t="s">
-        <v>482</v>
-      </c>
-      <c r="C184" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185" t="s">
-        <v>484</v>
-      </c>
-      <c r="B185" t="s">
-        <v>485</v>
-      </c>
-      <c r="C185" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" t="s">
-        <v>487</v>
-      </c>
-      <c r="B186" t="s">
-        <v>488</v>
-      </c>
-      <c r="C186" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187" t="s">
-        <v>490</v>
-      </c>
-      <c r="B187" t="s">
-        <v>491</v>
-      </c>
-      <c r="C187" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" t="s">
-        <v>493</v>
-      </c>
-      <c r="B188" t="s">
-        <v>494</v>
-      </c>
-      <c r="C188" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189" t="s">
-        <v>496</v>
-      </c>
-      <c r="B189" t="s">
-        <v>451</v>
-      </c>
-      <c r="C189" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" t="s">
-        <v>498</v>
-      </c>
-      <c r="B190" t="s">
-        <v>499</v>
-      </c>
-      <c r="C190" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" t="s">
-        <v>501</v>
-      </c>
-      <c r="B191" t="s">
-        <v>502</v>
-      </c>
-      <c r="C191" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" t="s">
-        <v>504</v>
-      </c>
-      <c r="B192" t="s">
-        <v>505</v>
-      </c>
-      <c r="C192" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" t="s">
-        <v>507</v>
-      </c>
-      <c r="B193" t="s">
-        <v>508</v>
-      </c>
-      <c r="C193" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" t="s">
-        <v>510</v>
-      </c>
-      <c r="B194" t="s">
-        <v>511</v>
-      </c>
-      <c r="C194" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="A195" t="s">
-        <v>513</v>
-      </c>
-      <c r="B195" t="s">
-        <v>514</v>
-      </c>
-      <c r="C195" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3">
-      <c r="A196" t="s">
-        <v>516</v>
-      </c>
-      <c r="B196" t="s">
-        <v>517</v>
-      </c>
-      <c r="C196" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3">
-      <c r="A197" t="s">
-        <v>519</v>
-      </c>
-      <c r="B197" t="s">
-        <v>520</v>
-      </c>
-      <c r="C197" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="A198" t="s">
-        <v>522</v>
-      </c>
-      <c r="B198" t="s">
-        <v>523</v>
-      </c>
-      <c r="C198" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" t="s">
-        <v>525</v>
-      </c>
-      <c r="B199" t="s">
-        <v>526</v>
-      </c>
-      <c r="C199" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" t="s">
-        <v>528</v>
-      </c>
-      <c r="B200" t="s">
-        <v>529</v>
-      </c>
-      <c r="C200" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201" t="s">
-        <v>531</v>
-      </c>
-      <c r="B201" t="s">
-        <v>532</v>
-      </c>
-      <c r="C201" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="A202" t="s">
-        <v>534</v>
-      </c>
-      <c r="B202" t="s">
-        <v>535</v>
-      </c>
-      <c r="C202" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" t="s">
-        <v>537</v>
-      </c>
-      <c r="B203" t="s">
-        <v>538</v>
-      </c>
-      <c r="C203" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" t="s">
-        <v>540</v>
-      </c>
-      <c r="B204" t="s">
-        <v>541</v>
-      </c>
-      <c r="C204" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" t="s">
-        <v>543</v>
-      </c>
-      <c r="B205" t="s">
-        <v>544</v>
-      </c>
-      <c r="C205" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" t="s">
-        <v>546</v>
-      </c>
-      <c r="B206" t="s">
-        <v>547</v>
-      </c>
-      <c r="C206" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3">
-      <c r="A207" t="s">
-        <v>549</v>
-      </c>
-      <c r="B207" t="s">
-        <v>550</v>
-      </c>
-      <c r="C207" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" t="s">
-        <v>552</v>
-      </c>
-      <c r="B208" t="s">
-        <v>553</v>
-      </c>
-      <c r="C208" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3">
-      <c r="A209" t="s">
-        <v>555</v>
-      </c>
-      <c r="B209" t="s">
-        <v>556</v>
-      </c>
-      <c r="C209" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3">
-      <c r="A210" t="s">
-        <v>558</v>
-      </c>
-      <c r="B210" t="s">
-        <v>559</v>
-      </c>
-      <c r="C210" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3">
-      <c r="A211" t="s">
-        <v>561</v>
-      </c>
-      <c r="B211" t="s">
-        <v>562</v>
-      </c>
-      <c r="C211" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3">
-      <c r="A212" t="s">
-        <v>564</v>
-      </c>
-      <c r="B212" t="s">
-        <v>565</v>
-      </c>
-      <c r="C212" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3">
+      <c r="E212" t="s">
+        <v>714</v>
+      </c>
+      <c r="F212" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>567</v>
+        <v>715</v>
       </c>
       <c r="B213" t="s">
-        <v>568</v>
+        <v>716</v>
       </c>
       <c r="C213" t="s">
-        <v>569</v>
+        <v>717</v>
+      </c>
+      <c r="F213" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
